--- a/docs/data/jp/xlsx/3891.xlsx
+++ b/docs/data/jp/xlsx/3891.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC176"/>
+  <dimension ref="A1:AC183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4295,10 +4298,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>5550</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4333,7 +4338,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>10698482</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5532,7 +5539,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5784,1003 +5791,1052 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>2735.915</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2634.186</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>3008.425</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>2637.133</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>2866.788</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>3070.691</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>3007.483</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>3260.376</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>3247.362</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>3131.752</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>3289.002</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>3652.132</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>3138.893</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>3065.681</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>3008.425</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>3007.483</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>3289.002</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>1059.267</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>843.758</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>550.038</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>1261.855</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>1448.665</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>900.579</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>840.571</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>1386.56</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>1452.811</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1411.476</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>1445.184</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>2401.447</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>1366.4</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>1015.759</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>550.038</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>840.571</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>1445.184</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>492.748</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>483.482</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>458.431</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>488.723</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>496.722</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>495.695</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>509.879</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>530.188</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>524.813</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>549.044</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>558.573</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>623.523</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>565.226</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>570.995</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>458.431</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>509.879</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>558.573</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>566.519</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>360.277</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>91.607</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>773.131</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>951.944</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>404.884</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>330.691</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>856.372</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>927.998</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>862.431</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>886.611</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>1777.923</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>801.173</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>444.765</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>91.607</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>330.691</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>886.611</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>4.112</v>
+        <v>492.748</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>3.879</v>
+        <v>483.482</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>7.705</v>
+        <v>458.431</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>4.367</v>
+        <v>488.723</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>7.396</v>
+        <v>496.722</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>4.709</v>
+        <v>495.695</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>11.647</v>
+        <v>509.879</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>4.007</v>
+        <v>530.188</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>10.077</v>
+        <v>524.813</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>4.151</v>
+        <v>549.044</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>11.512</v>
+        <v>558.573</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>3.456</v>
+        <v>623.523</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>1.717</v>
+        <v>565.226</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>3.05</v>
+        <v>570.995</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>7.705</v>
+        <v>458.431</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>11.647</v>
+        <v>509.879</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>11.512</v>
+        <v>558.573</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>3.724</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>5.452</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>4.969</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>6.632</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>6.993</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>566.519</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>360.277</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>91.607</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>773.131</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>951.944</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>404.884</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>330.691</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>856.372</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>927.998</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>862.431</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>886.611</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>1777.923</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>801.173</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>444.765</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>91.607</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>330.691</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>886.611</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>92.122</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>-70.655</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>82.004</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>120.49</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>-120.49</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>24.422</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>35.498</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>120.879</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>5.016</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>82.004</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>24.422</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>보상금 수취</t>
-        </is>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>1.866</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>1.866</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>물품 매각이익</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="n">
+        <v>4.112</v>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>3.879</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>7.705</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>0</v>
+        <v>4.367</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>0</v>
+        <v>7.396</v>
+      </c>
+      <c r="H87" s="22" t="n">
+        <v>4.709</v>
+      </c>
+      <c r="I87" s="22" t="n">
+        <v>11.647</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>16.023</v>
+        <v>4.007</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>0.927</v>
+        <v>10.077</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>4.151</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>11.512</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>10.797</v>
+        <v>3.456</v>
+      </c>
+      <c r="T87" s="22" t="n">
+        <v>1.717</v>
+      </c>
+      <c r="U87" s="22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V87" s="22" t="n">
+        <v>7.705</v>
+      </c>
+      <c r="W87" s="22" t="n">
+        <v>11.647</v>
+      </c>
+      <c r="X87" s="22" t="n">
+        <v>11.512</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>Insurance And Dividends Income NOI</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>0.791</v>
+        <v>0.533</v>
       </c>
       <c r="D88" s="22" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="E88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="22" t="n">
-        <v>0.224</v>
-      </c>
       <c r="F88" s="22" t="n">
-        <v>0.029</v>
+        <v>3.556</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>0</v>
+        <v>0.578</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1.6</v>
+        <v>5.452</v>
       </c>
       <c r="I88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>11.987</v>
+        <v>4.969</v>
       </c>
       <c r="K88" s="22" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="L88" s="22" t="n">
+        <v>6.632</v>
+      </c>
+      <c r="M88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="22" t="n">
+      <c r="N88" s="22" t="n">
+        <v>6.993</v>
+      </c>
+      <c r="T88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="22" t="n">
-        <v>4.617</v>
-      </c>
-      <c r="N88" s="22" t="n">
+      <c r="U88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>-1.223</v>
-      </c>
       <c r="V88" s="22" t="n">
-        <v>0.224</v>
+        <v>0</v>
       </c>
       <c r="W88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>4.617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="n">
+        <v>92.122</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>31.529</v>
+        <v>-70.655</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>12.785</v>
+        <v>82.004</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>120.49</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>-120.49</v>
       </c>
       <c r="H89" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>27.586</v>
-      </c>
-      <c r="L89" s="22" t="n">
-        <v>5.884</v>
+        <v>0</v>
+      </c>
+      <c r="J89" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>2.045</v>
+        <v>24.422</v>
+      </c>
+      <c r="N89" s="22" t="n">
+        <v>35.498</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>1.5</v>
+        <v>120.879</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>3.75</v>
+        <v>5.016</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>12.785</v>
+        <v>82.004</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>27.586</v>
+        <v>0</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>2.045</v>
+        <v>24.422</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="n">
-        <v>-4.521</v>
-      </c>
-      <c r="D90" s="22" t="n">
-        <v>4.271</v>
-      </c>
-      <c r="E90" s="22" t="n">
-        <v>16.748</v>
-      </c>
-      <c r="F90" s="22" t="n">
-        <v>4.289</v>
-      </c>
-      <c r="G90" s="22" t="n">
-        <v>3.264</v>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>4.793</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="I90" s="22" t="n">
-        <v>8.189</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>9.694000000000001</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>-3.384</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>24.569</v>
+        <v>0</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>2.458</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>4.096</v>
-      </c>
-      <c r="T90" s="22" t="n">
-        <v>4.151</v>
-      </c>
-      <c r="U90" s="22" t="n">
-        <v>7.708</v>
-      </c>
-      <c r="V90" s="22" t="n">
-        <v>16.748</v>
+        <v>1.866</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>8.189</v>
+        <v>0</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>2.458</v>
+        <v>1.866</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>102.085</v>
-      </c>
-      <c r="D91" s="22" t="n">
-        <v>-27.252</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>119.467</v>
+          <t>물품 매각이익</t>
+        </is>
       </c>
       <c r="F91" s="22" t="n">
-        <v>132.733</v>
+        <v>0</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>-102.129</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>16.555</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>47.423</v>
+        <v>0</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>46.682</v>
+        <v>16.023</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>11.997</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>137.016</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>46.919</v>
+        <v>0.927</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>60.842</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>130.047</v>
-      </c>
-      <c r="U91" s="22" t="n">
-        <v>18.303</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>119.467</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>47.423</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>46.919</v>
+        <v>10.797</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>Insurance And Dividends Income NOI</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>3.656</v>
+        <v>0.791</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>3.194</v>
+        <v>0</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>3.445</v>
+        <v>0.224</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>5.055</v>
+        <v>0.029</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>8.516</v>
+        <v>0</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>11.564</v>
+        <v>1.6</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>16.099</v>
+        <v>0</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>13.791</v>
+        <v>11.987</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>13.993</v>
+        <v>0</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>11.779</v>
+        <v>0</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>14.048</v>
+        <v>4.617</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>12.576</v>
+        <v>0</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>0.833</v>
+        <v>1.8</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>1.864</v>
+        <v>-1.223</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>3.445</v>
+        <v>0.224</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>16.099</v>
+        <v>0</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>14.048</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="C93" s="22" t="n">
-        <v>3.045</v>
+          <t>보조금 수입</t>
+        </is>
       </c>
       <c r="D93" s="22" t="n">
-        <v>4.926</v>
+        <v>31.529</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>30.45</v>
-      </c>
-      <c r="F93" s="22" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="G93" s="22" t="n">
-        <v>0.972</v>
+        <v>12.785</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>1.614</v>
+        <v>0</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>2.261</v>
-      </c>
-      <c r="J93" s="22" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="K93" s="22" t="n">
-        <v>2.932</v>
+        <v>27.586</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>3.363</v>
+        <v>5.884</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="N93" s="22" t="n">
-        <v>0.141</v>
+        <v>2.045</v>
       </c>
       <c r="T93" s="22" t="n">
-        <v>31.299</v>
+        <v>1.5</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>32.898</v>
+        <v>3.75</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>30.45</v>
+        <v>12.785</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>2.261</v>
+        <v>27.586</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>0.342</v>
+        <v>2.045</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>-4.521</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0</v>
+        <v>4.271</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0</v>
+        <v>16.748</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>0</v>
+        <v>4.289</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>86.59699999999999</v>
+        <v>3.264</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>-79.13200000000001</v>
+        <v>4.793</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>50.06</v>
+        <v>8.189</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>52.081</v>
+        <v>9.694000000000001</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>-18.998</v>
+        <v>-3.384</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>-33.083</v>
+        <v>24.569</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>0</v>
+        <v>2.458</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>0</v>
+        <v>4.096</v>
+      </c>
+      <c r="T94" s="22" t="n">
+        <v>4.151</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>7.708</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>0</v>
+        <v>16.748</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>50.06</v>
+        <v>8.189</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>0</v>
+        <v>2.458</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>-0.9350000000000001</v>
+        <v>102.085</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>2.119</v>
+        <v>-27.252</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>1.894</v>
+        <v>119.467</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>1.215</v>
+        <v>132.733</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>4.36</v>
+        <v>-102.129</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>0.317</v>
+        <v>16.555</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>0.596</v>
+        <v>47.423</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>0.963</v>
+        <v>46.682</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>6.167</v>
+        <v>11.997</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>0.586</v>
+        <v>137.016</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>0.139</v>
+        <v>46.919</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>0.014</v>
+        <v>60.842</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>0</v>
+        <v>130.047</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>0.074</v>
+        <v>18.303</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>1.894</v>
+        <v>119.467</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>0.596</v>
+        <v>47.423</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>0.139</v>
+        <v>46.919</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>5.766</v>
+        <v>3.656</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>10.239</v>
+        <v>3.194</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>35.789</v>
+        <v>3.445</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>6.313</v>
+        <v>5.055</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>100.446</v>
+        <v>8.516</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>-65.637</v>
+        <v>11.564</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>69.01600000000001</v>
+        <v>16.099</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>67.024</v>
+        <v>13.791</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>4.093</v>
+        <v>13.993</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>-17.355</v>
+        <v>11.779</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>14.529</v>
+        <v>14.048</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>12.732</v>
+        <v>12.576</v>
       </c>
       <c r="T96" s="22" t="n">
-        <v>32.131</v>
+        <v>0.833</v>
       </c>
       <c r="U96" s="22" t="n">
-        <v>34.835</v>
+        <v>1.864</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>35.789</v>
+        <v>3.445</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>69.01600000000001</v>
+        <v>16.099</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>14.529</v>
+        <v>14.048</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>662.838</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>322.786</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>175.286</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>899.55</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>749.369</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>487.076</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>309.098</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>836.03</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>935.902</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>1016.802</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>919.001</v>
-      </c>
-      <c r="N97" s="12" t="n">
-        <v>1826.034</v>
-      </c>
-      <c r="T97" s="12" t="n">
-        <v>899.0890000000001</v>
-      </c>
-      <c r="U97" s="12" t="n">
-        <v>428.231</v>
-      </c>
-      <c r="V97" s="12" t="n">
-        <v>175.286</v>
-      </c>
-      <c r="W97" s="12" t="n">
-        <v>309.098</v>
-      </c>
-      <c r="X97" s="12" t="n">
-        <v>919.001</v>
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>2.261</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="T97" s="22" t="n">
+        <v>31.299</v>
+      </c>
+      <c r="U97" s="22" t="n">
+        <v>32.898</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>2.261</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>0.342</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손실</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="D98" s="22" t="n">
@@ -6789,23 +6845,38 @@
       <c r="E98" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="F98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22" t="n">
+        <v>86.59699999999999</v>
+      </c>
       <c r="H98" s="22" t="n">
-        <v>0.539</v>
+        <v>-79.13200000000001</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>0.554</v>
+        <v>50.06</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>52.081</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <v>-18.998</v>
       </c>
       <c r="L98" s="22" t="n">
-        <v>0</v>
+        <v>-33.083</v>
       </c>
       <c r="M98" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="N98" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="V98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W98" s="22" t="n">
-        <v>0.554</v>
+        <v>50.06</v>
       </c>
       <c r="X98" s="22" t="n">
         <v>0</v>
@@ -6814,569 +6885,539 @@
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
+        <v>-0.9350000000000001</v>
       </c>
       <c r="D99" s="22" t="n">
+        <v>2.119</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <v>6.167</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>107.363</v>
+      <c r="U99" s="22" t="n">
+        <v>0.074</v>
       </c>
       <c r="V99" s="22" t="n">
-        <v>0</v>
+        <v>1.894</v>
       </c>
       <c r="W99" s="22" t="n">
-        <v>0.554</v>
+        <v>0.596</v>
       </c>
       <c r="X99" s="22" t="n">
-        <v>107.363</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n">
+        <v>5.766</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>10.239</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>35.789</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>6.313</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>100.446</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>-65.637</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>69.01600000000001</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>67.024</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>-17.355</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>14.529</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>12.732</v>
+      </c>
+      <c r="T100" s="22" t="n">
+        <v>32.131</v>
+      </c>
+      <c r="U100" s="22" t="n">
+        <v>34.835</v>
+      </c>
+      <c r="V100" s="22" t="n">
+        <v>35.789</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>69.01600000000001</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>14.529</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
         <v>662.838</v>
       </c>
-      <c r="D100" s="12" t="n">
+      <c r="D101" s="12" t="n">
         <v>322.786</v>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="E101" s="12" t="n">
         <v>175.286</v>
       </c>
-      <c r="F100" s="12" t="n">
+      <c r="F101" s="12" t="n">
         <v>899.55</v>
       </c>
-      <c r="G100" s="12" t="n">
-        <v>742.732</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>486.538</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>308.544</v>
-      </c>
-      <c r="J100" s="12" t="n">
+      <c r="G101" s="12" t="n">
+        <v>749.369</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>487.076</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>309.098</v>
+      </c>
+      <c r="J101" s="12" t="n">
         <v>836.03</v>
       </c>
-      <c r="K100" s="12" t="n">
+      <c r="K101" s="12" t="n">
         <v>935.902</v>
       </c>
-      <c r="L100" s="12" t="n">
+      <c r="L101" s="12" t="n">
         <v>1016.802</v>
       </c>
-      <c r="M100" s="12" t="n">
-        <v>811.638</v>
-      </c>
-      <c r="N100" s="12" t="n">
+      <c r="M101" s="12" t="n">
+        <v>919.001</v>
+      </c>
+      <c r="N101" s="12" t="n">
         <v>1826.034</v>
       </c>
-      <c r="T100" s="12" t="n">
-        <v>849.222</v>
-      </c>
-      <c r="U100" s="12" t="n">
+      <c r="T101" s="12" t="n">
+        <v>899.0890000000001</v>
+      </c>
+      <c r="U101" s="12" t="n">
         <v>428.231</v>
       </c>
-      <c r="V100" s="12" t="n">
+      <c r="V101" s="12" t="n">
         <v>175.286</v>
       </c>
-      <c r="W100" s="12" t="n">
-        <v>308.544</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>811.638</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C101" s="22" t="n">
-        <v>251.054</v>
-      </c>
-      <c r="D101" s="22" t="n">
-        <v>-35.221</v>
-      </c>
-      <c r="E101" s="22" t="n">
-        <v>97.148</v>
-      </c>
-      <c r="F101" s="22" t="n">
-        <v>181.606</v>
-      </c>
-      <c r="G101" s="22" t="n">
-        <v>314.584</v>
-      </c>
-      <c r="H101" s="22" t="n">
-        <v>7.141</v>
-      </c>
-      <c r="I101" s="22" t="n">
-        <v>185.547</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>121.998</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <v>410.673</v>
-      </c>
-      <c r="L101" s="22" t="n">
-        <v>145.75</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>343.984</v>
-      </c>
-      <c r="N101" s="22" t="n">
-        <v>412.834</v>
-      </c>
-      <c r="T101" s="22" t="n">
-        <v>401.501</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>244.298</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>97.148</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>185.547</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>343.984</v>
+      <c r="W101" s="12" t="n">
+        <v>309.098</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>919.001</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>-90.56999999999999</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>108.467</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>-52.085</v>
-      </c>
-      <c r="F102" s="22" t="n">
-        <v>59.997</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>-97.565</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>105.605</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>-100.604</v>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>116.55</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>-120.539</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>106.891</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>-167.916</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>146.147</v>
-      </c>
-      <c r="T102" s="22" t="n">
-        <v>-137.72</v>
-      </c>
-      <c r="U102" s="22" t="n">
-        <v>-122.054</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>-52.085</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>-100.604</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>-167.916</v>
+      <c r="A102" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G102" s="17">
+        <f>IF(OR(G101="",C101=""),"",IF(C101&lt;=0,"",IFERROR(G101/C101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H102" s="17">
+        <f>IF(OR(H101="",D101=""),"",IF(D101&lt;=0,"",IFERROR(H101/D101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I102" s="17">
+        <f>IF(OR(I101="",E101=""),"",IF(E101&lt;=0,"",IFERROR(I101/E101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J102" s="17">
+        <f>IF(OR(J101="",F101=""),"",IF(F101&lt;=0,"",IFERROR(J101/F101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF(OR(K101="",G101=""),"",IF(G101&lt;=0,"",IFERROR(K101/G101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L102" s="17">
+        <f>IF(OR(L101="",H101=""),"",IF(H101&lt;=0,"",IFERROR(L101/H101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M102" s="17">
+        <f>IF(OR(M101="",I101=""),"",IF(I101&lt;=0,"",IFERROR(M101/I101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N102" s="17">
+        <f>IF(OR(N101="",J101=""),"",IF(J101&lt;=0,"",IFERROR(N101/J101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T102" s="17">
+        <f>IF(OR(T101="",S101=""),"",IF(S101&lt;=0,"",IFERROR(T101/S101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U102" s="17">
+        <f>IF(OR(U101="",T101=""),"",IF(T101&lt;=0,"",IFERROR(U101/T101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V102" s="17">
+        <f>IF(OR(V101="",U101=""),"",IF(U101&lt;=0,"",IFERROR(V101/U101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W102" s="17">
+        <f>IF(OR(W101="",V101=""),"",IF(V101&lt;=0,"",IFERROR(W101/V101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X102" s="17">
+        <f>IF(OR(X101="",W101=""),"",IF(W101&lt;=0,"",IFERROR(X101/W101-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="n">
-        <v>160.483</v>
+          <t>투자유가증권 평가손실</t>
+        </is>
       </c>
       <c r="D103" s="22" t="n">
-        <v>73.246</v>
+        <v>0</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>45.064</v>
-      </c>
-      <c r="F103" s="22" t="n">
-        <v>241.603</v>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>217.018</v>
+        <v>0</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>112.747</v>
+        <v>0.539</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>84.94199999999999</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>238.549</v>
-      </c>
-      <c r="K103" s="22" t="n">
-        <v>290.132</v>
+        <v>0.554</v>
       </c>
       <c r="L103" s="22" t="n">
-        <v>252.642</v>
+        <v>0</v>
       </c>
       <c r="M103" s="22" t="n">
-        <v>176.067</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>558.981</v>
-      </c>
-      <c r="T103" s="22" t="n">
-        <v>263.78</v>
-      </c>
-      <c r="U103" s="22" t="n">
-        <v>122.243</v>
+        <v>0</v>
       </c>
       <c r="V103" s="22" t="n">
-        <v>45.064</v>
+        <v>0</v>
       </c>
       <c r="W103" s="22" t="n">
-        <v>84.94199999999999</v>
+        <v>0.554</v>
       </c>
       <c r="X103" s="22" t="n">
-        <v>176.067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="n">
-        <v>502.355</v>
-      </c>
-      <c r="D104" s="12" t="n">
-        <v>249.539</v>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>130.222</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>657.947</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>525.7140000000001</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>373.791</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>223.602</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>597.481</v>
-      </c>
-      <c r="K104" s="12" t="n">
-        <v>645.77</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>764.159</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>635.571</v>
-      </c>
-      <c r="N104" s="12" t="n">
-        <v>1267.052</v>
-      </c>
-      <c r="T104" s="12" t="n">
-        <v>585.442</v>
-      </c>
-      <c r="U104" s="12" t="n">
-        <v>305.988</v>
-      </c>
-      <c r="V104" s="12" t="n">
-        <v>130.222</v>
-      </c>
-      <c r="W104" s="12" t="n">
-        <v>223.602</v>
-      </c>
-      <c r="X104" s="12" t="n">
-        <v>635.571</v>
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="22" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="I104" s="22" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="L104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="22" t="n">
+        <v>107.363</v>
+      </c>
+      <c r="V104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="22" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="X104" s="22" t="n">
+        <v>107.363</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>502.355</v>
+        <v>662.838</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>249.539</v>
+        <v>322.786</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>130.222</v>
+        <v>175.286</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>657.947</v>
+        <v>899.55</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>525.7140000000001</v>
+        <v>742.732</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>373.791</v>
+        <v>486.538</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>223.602</v>
+        <v>308.544</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>597.481</v>
+        <v>836.03</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>645.77</v>
+        <v>935.902</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>764.159</v>
+        <v>1016.802</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>635.571</v>
+        <v>811.638</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>1267.052</v>
+        <v>1826.034</v>
       </c>
       <c r="T105" s="12" t="n">
-        <v>585.442</v>
+        <v>849.222</v>
       </c>
       <c r="U105" s="12" t="n">
-        <v>305.988</v>
+        <v>428.231</v>
       </c>
       <c r="V105" s="12" t="n">
-        <v>130.222</v>
+        <v>175.286</v>
       </c>
       <c r="W105" s="12" t="n">
-        <v>223.602</v>
+        <v>308.544</v>
       </c>
       <c r="X105" s="12" t="n">
-        <v>635.571</v>
+        <v>811.638</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>251.054</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>-35.221</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>97.148</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>181.606</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>314.584</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>7.141</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>185.547</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>121.998</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>410.673</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>343.984</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>412.834</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>401.501</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>244.298</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>97.148</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>185.547</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>343.984</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B107" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-      <c r="J107" s="18" t="n"/>
-      <c r="K107" s="18" t="n"/>
-      <c r="L107" s="18" t="n"/>
-      <c r="M107" s="18" t="n"/>
-      <c r="N107" s="18" t="n"/>
-      <c r="O107" s="18" t="n"/>
-      <c r="P107" s="18" t="n"/>
-      <c r="Q107" s="18" t="n"/>
-      <c r="R107" s="18" t="n"/>
-      <c r="S107" s="18" t="n"/>
-      <c r="T107" s="18" t="n"/>
-      <c r="U107" s="18" t="n"/>
-      <c r="V107" s="18" t="n"/>
-      <c r="W107" s="18" t="n"/>
-      <c r="X107" s="18" t="n"/>
-      <c r="Y107" s="18" t="n"/>
-      <c r="Z107" s="18" t="n"/>
-      <c r="AA107" s="18" t="n"/>
-      <c r="AB107" s="18" t="n"/>
-      <c r="AC107" s="18" t="n"/>
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>-90.56999999999999</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>108.467</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>-52.085</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>59.997</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>-97.565</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>105.605</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>-100.604</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>-120.539</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>106.891</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>-167.916</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>146.147</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>-137.72</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>-122.054</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>-52.085</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>-100.604</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>-167.916</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M108" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N108" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O108" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P108" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q108" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R108" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S108" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T108" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U108" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V108" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W108" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X108" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y108" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z108" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA108" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB108" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC108" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="n">
+        <v>160.483</v>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>73.246</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>45.064</v>
+      </c>
+      <c r="F108" s="22" t="n">
+        <v>241.603</v>
+      </c>
+      <c r="G108" s="22" t="n">
+        <v>217.018</v>
+      </c>
+      <c r="H108" s="22" t="n">
+        <v>112.747</v>
+      </c>
+      <c r="I108" s="22" t="n">
+        <v>84.94199999999999</v>
+      </c>
+      <c r="J108" s="22" t="n">
+        <v>238.549</v>
+      </c>
+      <c r="K108" s="22" t="n">
+        <v>290.132</v>
+      </c>
+      <c r="L108" s="22" t="n">
+        <v>252.642</v>
+      </c>
+      <c r="M108" s="22" t="n">
+        <v>176.067</v>
+      </c>
+      <c r="N108" s="22" t="n">
+        <v>558.981</v>
+      </c>
+      <c r="T108" s="22" t="n">
+        <v>263.78</v>
+      </c>
+      <c r="U108" s="22" t="n">
+        <v>122.243</v>
+      </c>
+      <c r="V108" s="22" t="n">
+        <v>45.064</v>
+      </c>
+      <c r="W108" s="22" t="n">
+        <v>84.94199999999999</v>
+      </c>
+      <c r="X108" s="22" t="n">
+        <v>176.067</v>
       </c>
     </row>
     <row r="109">
@@ -7438,2679 +7479,3109 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C110" s="22" t="n">
-        <v>13.085</v>
-      </c>
-      <c r="D110" s="22" t="n">
-        <v>-14.758</v>
-      </c>
-      <c r="E110" s="22" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="F110" s="22" t="n">
-        <v>4.142</v>
-      </c>
-      <c r="G110" s="22" t="n">
-        <v>-20.661</v>
-      </c>
-      <c r="H110" s="22" t="n">
-        <v>19.274</v>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="J110" s="22" t="n">
-        <v>5.897</v>
-      </c>
-      <c r="K110" s="22" t="n">
-        <v>45.959</v>
-      </c>
-      <c r="L110" s="22" t="n">
-        <v>32.712</v>
-      </c>
-      <c r="M110" s="22" t="n">
-        <v>32.992</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>147.256</v>
-      </c>
-      <c r="T110" s="22" t="n">
-        <v>-1.097</v>
-      </c>
-      <c r="U110" s="22" t="n">
-        <v>3.703</v>
-      </c>
-      <c r="V110" s="22" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="W110" s="22" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>32.992</v>
+      <c r="A110" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G110" s="17">
+        <f>IF(OR(G109="",C109=""),"",IF(C109&lt;=0,"",IFERROR(G109/C109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H110" s="17">
+        <f>IF(OR(H109="",D109=""),"",IF(D109&lt;=0,"",IFERROR(H109/D109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I110" s="17">
+        <f>IF(OR(I109="",E109=""),"",IF(E109&lt;=0,"",IFERROR(I109/E109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J110" s="17">
+        <f>IF(OR(J109="",F109=""),"",IF(F109&lt;=0,"",IFERROR(J109/F109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF(OR(K109="",G109=""),"",IF(G109&lt;=0,"",IFERROR(K109/G109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L110" s="17">
+        <f>IF(OR(L109="",H109=""),"",IF(H109&lt;=0,"",IFERROR(L109/H109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M110" s="17">
+        <f>IF(OR(M109="",I109=""),"",IF(I109&lt;=0,"",IFERROR(M109/I109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N110" s="17">
+        <f>IF(OR(N109="",J109=""),"",IF(J109&lt;=0,"",IFERROR(N109/J109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T110" s="17">
+        <f>IF(OR(T109="",S109=""),"",IF(S109&lt;=0,"",IFERROR(T109/S109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U110" s="17">
+        <f>IF(OR(U109="",T109=""),"",IF(T109&lt;=0,"",IFERROR(U109/T109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V110" s="17">
+        <f>IF(OR(V109="",U109=""),"",IF(U109&lt;=0,"",IFERROR(V109/U109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W110" s="17">
+        <f>IF(OR(W109="",V109=""),"",IF(V109&lt;=0,"",IFERROR(W109/V109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X110" s="17">
+        <f>IF(OR(X109="",W109=""),"",IF(W109&lt;=0,"",IFERROR(X109/W109-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>25.379</v>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>35.737</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>-39.088</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>42.146</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>83.03400000000001</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>17.531</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>35.205</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>-48.529</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>-0.413</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>39.387</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>122.347</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>35.726</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>30.103</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>-43.156</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>-39.088</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>35.205</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>122.347</v>
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>502.355</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>249.539</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>130.222</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>657.947</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>525.7140000000001</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>373.791</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>223.602</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>597.481</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>645.77</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>764.159</v>
+      </c>
+      <c r="M111" s="12" t="n">
+        <v>635.571</v>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>1267.052</v>
+      </c>
+      <c r="T111" s="12" t="n">
+        <v>585.442</v>
+      </c>
+      <c r="U111" s="12" t="n">
+        <v>305.988</v>
+      </c>
+      <c r="V111" s="12" t="n">
+        <v>130.222</v>
+      </c>
+      <c r="W111" s="12" t="n">
+        <v>223.602</v>
+      </c>
+      <c r="X111" s="12" t="n">
+        <v>635.571</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여 조정액</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="n">
-        <v>3.902</v>
-      </c>
-      <c r="D112" s="22" t="n">
-        <v>3.902</v>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>177.234</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>-0.328</v>
-      </c>
-      <c r="G112" s="22" t="n">
-        <v>-0.328</v>
-      </c>
-      <c r="H112" s="22" t="n">
-        <v>-0.329</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>284.494</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>-6.21</v>
-      </c>
-      <c r="K112" s="22" t="n">
-        <v>-6.21</v>
-      </c>
-      <c r="L112" s="22" t="n">
-        <v>-6.21</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>218.487</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>-17.609</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>-0.671</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>-59.056</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>177.234</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>284.494</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>218.487</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n">
-        <v>42.366</v>
-      </c>
-      <c r="D113" s="22" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>161.437</v>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>45.961</v>
-      </c>
-      <c r="G113" s="22" t="n">
-        <v>62.043</v>
-      </c>
-      <c r="H113" s="22" t="n">
-        <v>36.478</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>321.924</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>-48.842</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>39.336</v>
-      </c>
-      <c r="L113" s="22" t="n">
-        <v>65.889</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>373.826</v>
-      </c>
-      <c r="N113" s="22" t="n">
-        <v>165.373</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>28.335</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>-98.512</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>161.437</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>321.924</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>373.826</v>
+      <c r="A112" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G112" s="17">
+        <f>IF(OR(G111="",C111=""),"",IF(C111&lt;=0,"",IFERROR(G111/C111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H112" s="17">
+        <f>IF(OR(H111="",D111=""),"",IF(D111&lt;=0,"",IFERROR(H111/D111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I112" s="17">
+        <f>IF(OR(I111="",E111=""),"",IF(E111&lt;=0,"",IFERROR(I111/E111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J112" s="17">
+        <f>IF(OR(J111="",F111=""),"",IF(F111&lt;=0,"",IFERROR(J111/F111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF(OR(K111="",G111=""),"",IF(G111&lt;=0,"",IFERROR(K111/G111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L112" s="17">
+        <f>IF(OR(L111="",H111=""),"",IF(H111&lt;=0,"",IFERROR(L111/H111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M112" s="17">
+        <f>IF(OR(M111="",I111=""),"",IF(I111&lt;=0,"",IFERROR(M111/I111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N112" s="17">
+        <f>IF(OR(N111="",J111=""),"",IF(J111&lt;=0,"",IFERROR(N111/J111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T112" s="17">
+        <f>IF(OR(T111="",S111=""),"",IF(S111&lt;=0,"",IFERROR(T111/S111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U112" s="17">
+        <f>IF(OR(U111="",T111=""),"",IF(T111&lt;=0,"",IFERROR(U111/T111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V112" s="17">
+        <f>IF(OR(V111="",U111=""),"",IF(U111&lt;=0,"",IFERROR(V111/U111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W112" s="17">
+        <f>IF(OR(W111="",V111=""),"",IF(V111&lt;=0,"",IFERROR(W111/V111-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X112" s="17">
+        <f>IF(OR(X111="",W111=""),"",IF(W111&lt;=0,"",IFERROR(X111/W111-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="n">
-        <v>544.72</v>
-      </c>
-      <c r="D114" s="12" t="n">
-        <v>274.419</v>
-      </c>
-      <c r="E114" s="12" t="n">
-        <v>291.66</v>
-      </c>
-      <c r="F114" s="12" t="n">
-        <v>703.908</v>
-      </c>
-      <c r="G114" s="12" t="n">
-        <v>587.758</v>
-      </c>
-      <c r="H114" s="12" t="n">
-        <v>410.268</v>
-      </c>
-      <c r="I114" s="12" t="n">
-        <v>545.526</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>548.639</v>
-      </c>
-      <c r="K114" s="12" t="n">
-        <v>685.105</v>
-      </c>
-      <c r="L114" s="12" t="n">
-        <v>830.049</v>
-      </c>
-      <c r="M114" s="12" t="n">
-        <v>1009.397</v>
-      </c>
-      <c r="N114" s="12" t="n">
-        <v>1432.426</v>
-      </c>
-      <c r="T114" s="12" t="n">
-        <v>613.777</v>
-      </c>
-      <c r="U114" s="12" t="n">
-        <v>207.477</v>
-      </c>
-      <c r="V114" s="12" t="n">
-        <v>291.66</v>
-      </c>
-      <c r="W114" s="12" t="n">
-        <v>545.526</v>
-      </c>
-      <c r="X114" s="12" t="n">
-        <v>1009.397</v>
-      </c>
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B114" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="18" t="n"/>
+      <c r="F114" s="18" t="n"/>
+      <c r="G114" s="18" t="n"/>
+      <c r="H114" s="18" t="n"/>
+      <c r="I114" s="18" t="n"/>
+      <c r="J114" s="18" t="n"/>
+      <c r="K114" s="18" t="n"/>
+      <c r="L114" s="18" t="n"/>
+      <c r="M114" s="18" t="n"/>
+      <c r="N114" s="18" t="n"/>
+      <c r="O114" s="18" t="n"/>
+      <c r="P114" s="18" t="n"/>
+      <c r="Q114" s="18" t="n"/>
+      <c r="R114" s="18" t="n"/>
+      <c r="S114" s="18" t="n"/>
+      <c r="T114" s="18" t="n"/>
+      <c r="U114" s="18" t="n"/>
+      <c r="V114" s="18" t="n"/>
+      <c r="W114" s="18" t="n"/>
+      <c r="X114" s="18" t="n"/>
+      <c r="Y114" s="18" t="n"/>
+      <c r="Z114" s="18" t="n"/>
+      <c r="AA114" s="18" t="n"/>
+      <c r="AB114" s="18" t="n"/>
+      <c r="AC114" s="18" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="n">
-        <v>544.72</v>
-      </c>
-      <c r="D115" s="12" t="n">
-        <v>274.419</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>291.66</v>
-      </c>
-      <c r="F115" s="12" t="n">
-        <v>703.908</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>587.758</v>
-      </c>
-      <c r="H115" s="12" t="n">
-        <v>410.268</v>
-      </c>
-      <c r="I115" s="12" t="n">
-        <v>545.526</v>
-      </c>
-      <c r="J115" s="12" t="n">
-        <v>548.639</v>
-      </c>
-      <c r="K115" s="12" t="n">
-        <v>685.105</v>
-      </c>
-      <c r="L115" s="12" t="n">
-        <v>830.049</v>
-      </c>
-      <c r="M115" s="12" t="n">
-        <v>1009.397</v>
-      </c>
-      <c r="N115" s="12" t="n">
-        <v>1432.426</v>
-      </c>
-      <c r="T115" s="12" t="n">
-        <v>613.777</v>
-      </c>
-      <c r="U115" s="12" t="n">
-        <v>207.477</v>
-      </c>
-      <c r="V115" s="12" t="n">
-        <v>291.66</v>
-      </c>
-      <c r="W115" s="12" t="n">
-        <v>545.526</v>
-      </c>
-      <c r="X115" s="12" t="n">
-        <v>1009.397</v>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O115" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q115" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S115" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T115" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U115" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V115" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W115" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X115" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y115" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z115" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA115" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB115" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC115" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>502.355</v>
+      </c>
+      <c r="D116" s="12" t="n">
+        <v>249.539</v>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>130.222</v>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>657.947</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>525.7140000000001</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>373.791</v>
+      </c>
+      <c r="I116" s="12" t="n">
+        <v>223.602</v>
+      </c>
+      <c r="J116" s="12" t="n">
+        <v>597.481</v>
+      </c>
+      <c r="K116" s="12" t="n">
+        <v>645.77</v>
+      </c>
+      <c r="L116" s="12" t="n">
+        <v>764.159</v>
+      </c>
+      <c r="M116" s="12" t="n">
+        <v>635.571</v>
+      </c>
+      <c r="N116" s="12" t="n">
+        <v>1267.052</v>
+      </c>
+      <c r="T116" s="12" t="n">
+        <v>585.442</v>
+      </c>
+      <c r="U116" s="12" t="n">
+        <v>305.988</v>
+      </c>
+      <c r="V116" s="12" t="n">
+        <v>130.222</v>
+      </c>
+      <c r="W116" s="12" t="n">
+        <v>223.602</v>
+      </c>
+      <c r="X116" s="12" t="n">
+        <v>635.571</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="n">
+        <v>13.085</v>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>-14.758</v>
+      </c>
+      <c r="E117" s="22" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="F117" s="22" t="n">
+        <v>4.142</v>
+      </c>
+      <c r="G117" s="22" t="n">
+        <v>-20.661</v>
+      </c>
+      <c r="H117" s="22" t="n">
+        <v>19.274</v>
+      </c>
+      <c r="I117" s="22" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>5.897</v>
+      </c>
+      <c r="K117" s="22" t="n">
+        <v>45.959</v>
+      </c>
+      <c r="L117" s="22" t="n">
+        <v>32.712</v>
+      </c>
+      <c r="M117" s="22" t="n">
+        <v>32.992</v>
+      </c>
+      <c r="N117" s="22" t="n">
+        <v>147.256</v>
+      </c>
+      <c r="T117" s="22" t="n">
+        <v>-1.097</v>
+      </c>
+      <c r="U117" s="22" t="n">
+        <v>3.703</v>
+      </c>
+      <c r="V117" s="22" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="W117" s="22" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="X117" s="22" t="n">
+        <v>32.992</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C118" s="22" t="n">
+        <v>25.379</v>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>35.737</v>
+      </c>
+      <c r="E118" s="22" t="n">
+        <v>-39.088</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>42.146</v>
+      </c>
+      <c r="G118" s="22" t="n">
+        <v>83.03400000000001</v>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>17.531</v>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>35.205</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>-48.529</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>-0.413</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>39.387</v>
+      </c>
+      <c r="M118" s="22" t="n">
+        <v>122.347</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>35.726</v>
+      </c>
+      <c r="T118" s="22" t="n">
+        <v>30.103</v>
+      </c>
+      <c r="U118" s="22" t="n">
+        <v>-43.156</v>
+      </c>
+      <c r="V118" s="22" t="n">
+        <v>-39.088</v>
+      </c>
+      <c r="W118" s="22" t="n">
+        <v>35.205</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>122.347</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여 조정액</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>177.234</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>-0.328</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>-0.328</v>
+      </c>
+      <c r="H119" s="22" t="n">
+        <v>-0.329</v>
+      </c>
+      <c r="I119" s="22" t="n">
+        <v>284.494</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="L119" s="22" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="M119" s="22" t="n">
+        <v>218.487</v>
+      </c>
+      <c r="N119" s="22" t="n">
+        <v>-17.609</v>
+      </c>
+      <c r="T119" s="22" t="n">
+        <v>-0.671</v>
+      </c>
+      <c r="U119" s="22" t="n">
+        <v>-59.056</v>
+      </c>
+      <c r="V119" s="22" t="n">
+        <v>177.234</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>284.494</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>218.487</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="n">
+        <v>42.366</v>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>161.437</v>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>45.961</v>
+      </c>
+      <c r="G120" s="22" t="n">
+        <v>62.043</v>
+      </c>
+      <c r="H120" s="22" t="n">
+        <v>36.478</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>321.924</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>-48.842</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <v>39.336</v>
+      </c>
+      <c r="L120" s="22" t="n">
+        <v>65.889</v>
+      </c>
+      <c r="M120" s="22" t="n">
+        <v>373.826</v>
+      </c>
+      <c r="N120" s="22" t="n">
+        <v>165.373</v>
+      </c>
+      <c r="T120" s="22" t="n">
+        <v>28.335</v>
+      </c>
+      <c r="U120" s="22" t="n">
+        <v>-98.512</v>
+      </c>
+      <c r="V120" s="22" t="n">
+        <v>161.437</v>
+      </c>
+      <c r="W120" s="22" t="n">
+        <v>321.924</v>
+      </c>
+      <c r="X120" s="22" t="n">
+        <v>373.826</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>544.72</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>274.419</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>291.66</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>703.908</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>587.758</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>410.268</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <v>545.526</v>
+      </c>
+      <c r="J121" s="12" t="n">
+        <v>548.639</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>685.105</v>
+      </c>
+      <c r="L121" s="12" t="n">
+        <v>830.049</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>1009.397</v>
+      </c>
+      <c r="N121" s="12" t="n">
+        <v>1432.426</v>
+      </c>
+      <c r="T121" s="12" t="n">
+        <v>613.777</v>
+      </c>
+      <c r="U121" s="12" t="n">
+        <v>207.477</v>
+      </c>
+      <c r="V121" s="12" t="n">
+        <v>291.66</v>
+      </c>
+      <c r="W121" s="12" t="n">
+        <v>545.526</v>
+      </c>
+      <c r="X121" s="12" t="n">
+        <v>1009.397</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>544.72</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>274.419</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>291.66</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>703.908</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>587.758</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>410.268</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>545.526</v>
+      </c>
+      <c r="J122" s="12" t="n">
+        <v>548.639</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>685.105</v>
+      </c>
+      <c r="L122" s="12" t="n">
+        <v>830.049</v>
+      </c>
+      <c r="M122" s="12" t="n">
+        <v>1009.397</v>
+      </c>
+      <c r="N122" s="12" t="n">
+        <v>1432.426</v>
+      </c>
+      <c r="T122" s="12" t="n">
+        <v>613.777</v>
+      </c>
+      <c r="U122" s="12" t="n">
+        <v>207.477</v>
+      </c>
+      <c r="V122" s="12" t="n">
+        <v>291.66</v>
+      </c>
+      <c r="W122" s="12" t="n">
+        <v>545.526</v>
+      </c>
+      <c r="X122" s="12" t="n">
+        <v>1009.397</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C116" s="12" t="n">
+      <c r="C123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="12" t="n">
+      <c r="D123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="12" t="n">
+      <c r="E123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="12" t="n">
+      <c r="F123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="12" t="n">
+      <c r="G123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="12" t="n">
+      <c r="H123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="12" t="n">
+      <c r="I123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="12" t="n">
+      <c r="J123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K116" s="12" t="n">
+      <c r="K123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L116" s="12" t="n">
+      <c r="L123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M116" s="12" t="n">
+      <c r="M123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N116" s="12" t="n">
+      <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="12" t="n">
+      <c r="T123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="U116" s="12" t="n">
+      <c r="U123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="12" t="n">
+      <c r="V123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="12" t="n">
+      <c r="W123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="12" t="n">
+      <c r="X123" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B118" s="44" t="inlineStr">
+      <c r="B125" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C118" s="18" t="n"/>
-      <c r="D118" s="18" t="n"/>
-      <c r="E118" s="18" t="n"/>
-      <c r="F118" s="18" t="n"/>
-      <c r="G118" s="18" t="n"/>
-      <c r="H118" s="18" t="n"/>
-      <c r="I118" s="18" t="n"/>
-      <c r="J118" s="18" t="n"/>
-      <c r="K118" s="18" t="n"/>
-      <c r="L118" s="18" t="n"/>
-      <c r="M118" s="18" t="n"/>
-      <c r="N118" s="18" t="n"/>
-      <c r="O118" s="18" t="n"/>
-      <c r="P118" s="18" t="n"/>
-      <c r="Q118" s="18" t="n"/>
-      <c r="R118" s="18" t="n"/>
-      <c r="S118" s="18" t="n"/>
-      <c r="T118" s="18" t="n"/>
-      <c r="U118" s="18" t="n"/>
-      <c r="V118" s="18" t="n"/>
-      <c r="W118" s="18" t="n"/>
-      <c r="X118" s="18" t="n"/>
-      <c r="Y118" s="18" t="n"/>
-      <c r="Z118" s="18" t="n"/>
-      <c r="AA118" s="18" t="n"/>
-      <c r="AB118" s="18" t="n"/>
-      <c r="AC118" s="18" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="C125" s="18" t="n"/>
+      <c r="D125" s="18" t="n"/>
+      <c r="E125" s="18" t="n"/>
+      <c r="F125" s="18" t="n"/>
+      <c r="G125" s="18" t="n"/>
+      <c r="H125" s="18" t="n"/>
+      <c r="I125" s="18" t="n"/>
+      <c r="J125" s="18" t="n"/>
+      <c r="K125" s="18" t="n"/>
+      <c r="L125" s="18" t="n"/>
+      <c r="M125" s="18" t="n"/>
+      <c r="N125" s="18" t="n"/>
+      <c r="O125" s="18" t="n"/>
+      <c r="P125" s="18" t="n"/>
+      <c r="Q125" s="18" t="n"/>
+      <c r="R125" s="18" t="n"/>
+      <c r="S125" s="18" t="n"/>
+      <c r="T125" s="18" t="n"/>
+      <c r="U125" s="18" t="n"/>
+      <c r="V125" s="18" t="n"/>
+      <c r="W125" s="18" t="n"/>
+      <c r="X125" s="18" t="n"/>
+      <c r="Y125" s="18" t="n"/>
+      <c r="Z125" s="18" t="n"/>
+      <c r="AA125" s="18" t="n"/>
+      <c r="AB125" s="18" t="n"/>
+      <c r="AC125" s="18" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E126" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H126" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr">
+      <c r="J126" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr">
+      <c r="K126" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L119" s="5" t="inlineStr">
+      <c r="L126" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M119" s="5" t="inlineStr">
+      <c r="M126" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N119" s="5" t="inlineStr">
+      <c r="N126" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O119" s="5" t="inlineStr">
+      <c r="O126" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P119" s="5" t="inlineStr">
+      <c r="P126" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q119" s="5" t="inlineStr">
+      <c r="Q126" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R119" s="5" t="inlineStr">
+      <c r="R126" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S119" s="5" t="inlineStr">
+      <c r="S126" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T119" s="5" t="inlineStr">
+      <c r="T126" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U119" s="5" t="inlineStr">
+      <c r="U126" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V119" s="5" t="inlineStr">
+      <c r="V126" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W119" s="5" t="inlineStr">
+      <c r="W126" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X119" s="5" t="inlineStr">
+      <c r="X126" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y119" s="5" t="inlineStr">
+      <c r="Y126" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z119" s="5" t="inlineStr">
+      <c r="Z126" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA119" s="5" t="inlineStr">
+      <c r="AA126" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB119" s="5" t="inlineStr">
+      <c r="AB126" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC119" s="5" t="inlineStr">
+      <c r="AC126" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="E120" s="12" t="n">
+      <c r="E127" s="12" t="n">
         <v>2021.304</v>
       </c>
-      <c r="I120" s="12" t="n">
+      <c r="I127" s="12" t="n">
         <v>2437.364</v>
       </c>
-      <c r="M120" s="12" t="n">
+      <c r="M127" s="12" t="n">
         <v>3600.372</v>
       </c>
-      <c r="O120" s="12" t="n">
+      <c r="O127" s="12" t="n">
         <v>-306.935</v>
       </c>
-      <c r="P120" s="12" t="n">
+      <c r="P127" s="12" t="n">
         <v>855.774</v>
       </c>
-      <c r="Q120" s="12" t="n">
+      <c r="Q127" s="12" t="n">
         <v>1436.824</v>
       </c>
-      <c r="R120" s="12" t="n">
+      <c r="R127" s="12" t="n">
         <v>970.703</v>
       </c>
-      <c r="S120" s="12" t="n">
+      <c r="S127" s="12" t="n">
         <v>2784.323</v>
       </c>
-      <c r="T120" s="12" t="n">
+      <c r="T127" s="12" t="n">
         <v>4182.869</v>
       </c>
-      <c r="U120" s="12" t="n">
+      <c r="U127" s="12" t="n">
         <v>3532.86</v>
       </c>
-      <c r="V120" s="12" t="n">
+      <c r="V127" s="12" t="n">
         <v>2021.304</v>
       </c>
-      <c r="W120" s="12" t="n">
+      <c r="W127" s="12" t="n">
         <v>2437.364</v>
       </c>
-      <c r="X120" s="12" t="n">
+      <c r="X127" s="12" t="n">
         <v>3600.372</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E121" s="22" t="n">
-        <v>1426.934</v>
-      </c>
-      <c r="I121" s="22" t="n">
-        <v>1030.84</v>
-      </c>
-      <c r="M121" s="22" t="n">
-        <v>1421.29</v>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>1572.375</v>
-      </c>
-      <c r="P121" s="22" t="n">
-        <v>1407.956</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>1194.562</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>1254.79</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>1279.116</v>
-      </c>
-      <c r="T121" s="22" t="n">
-        <v>1359.946</v>
-      </c>
-      <c r="U121" s="22" t="n">
-        <v>1409.579</v>
-      </c>
-      <c r="V121" s="22" t="n">
-        <v>1426.934</v>
-      </c>
-      <c r="W121" s="22" t="n">
-        <v>1030.84</v>
-      </c>
-      <c r="X121" s="22" t="n">
-        <v>1421.29</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="O122" s="22" t="n">
-        <v>532.049</v>
-      </c>
-      <c r="P122" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>관계회사 정리이익</t>
-        </is>
-      </c>
-      <c r="P123" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>-123.744</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>107.363</v>
-      </c>
-      <c r="O124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" s="22" t="n">
-        <v>848.225</v>
-      </c>
-      <c r="Q124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>12.009</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>49.866</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>107.363</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>재해손실</t>
-        </is>
-      </c>
-      <c r="O125" s="22" t="n">
-        <v>172.505</v>
-      </c>
-      <c r="P125" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>보상금 수취</t>
-        </is>
-      </c>
-      <c r="I126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="22" t="n">
-        <v>-60.158</v>
-      </c>
-      <c r="W126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" s="22" t="n">
-        <v>-60.158</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>-53.362</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>-34.709</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>-11.679</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>-53.362</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>-34.709</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>-11.679</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>보험금 수익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E128" s="22" t="n">
-        <v>-1.015</v>
+        <v>1426.934</v>
       </c>
       <c r="I128" s="22" t="n">
-        <v>-1.629</v>
+        <v>1030.84</v>
       </c>
       <c r="M128" s="22" t="n">
-        <v>-16.604</v>
+        <v>1421.29</v>
       </c>
       <c r="O128" s="22" t="n">
-        <v>-11.858</v>
+        <v>1572.375</v>
       </c>
       <c r="P128" s="22" t="n">
-        <v>-170.867</v>
+        <v>1407.956</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>-14.268</v>
+        <v>1194.562</v>
       </c>
       <c r="R128" s="22" t="n">
-        <v>-15.099</v>
+        <v>1254.79</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>-12.122</v>
+        <v>1279.116</v>
       </c>
       <c r="T128" s="22" t="n">
-        <v>-4.298</v>
+        <v>1359.946</v>
       </c>
       <c r="U128" s="22" t="n">
-        <v>-0.075</v>
+        <v>1409.579</v>
       </c>
       <c r="V128" s="22" t="n">
-        <v>-1.015</v>
+        <v>1426.934</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>-1.629</v>
+        <v>1030.84</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>-16.604</v>
+        <v>1421.29</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 증감</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="O129" s="22" t="n">
-        <v>28.824</v>
+        <v>532.049</v>
       </c>
       <c r="P129" s="22" t="n">
-        <v>-6.781</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="R129" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여자산 증감</t>
-        </is>
-      </c>
-      <c r="E130" s="22" t="n">
+          <t>관계회사 정리이익</t>
+        </is>
+      </c>
+      <c r="P130" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I130" s="22" t="n">
-        <v>-80.547</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>-104.594</v>
-      </c>
-      <c r="V130" s="22" t="n">
+      <c r="Q130" s="22" t="n">
+        <v>-123.744</v>
+      </c>
+      <c r="R130" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="W130" s="22" t="n">
-        <v>-80.547</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>-104.594</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>-70.854</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>-67.399</v>
+        <v>0</v>
       </c>
       <c r="M131" s="22" t="n">
+        <v>107.363</v>
+      </c>
+      <c r="O131" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O131" s="22" t="n">
-        <v>61.438</v>
-      </c>
       <c r="P131" s="22" t="n">
-        <v>3.118</v>
+        <v>848.225</v>
       </c>
       <c r="Q131" s="22" t="n">
-        <v>14.004</v>
+        <v>0</v>
       </c>
       <c r="R131" s="22" t="n">
-        <v>-0.979</v>
+        <v>0</v>
       </c>
       <c r="S131" s="22" t="n">
-        <v>19.076</v>
+        <v>12.009</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>-683.3869999999999</v>
+        <v>49.866</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-197.694</v>
-      </c>
-      <c r="V131" s="22" t="n">
-        <v>-70.854</v>
+        <v>0</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>-67.399</v>
+        <v>0</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>0</v>
+        <v>107.363</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="E132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="22" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" s="22" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="X132" s="22" t="n">
+          <t>재해손실</t>
+        </is>
+      </c>
+      <c r="O132" s="22" t="n">
+        <v>172.505</v>
+      </c>
+      <c r="P132" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="E133" s="22" t="n">
-        <v>19.346</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="I133" s="22" t="n">
-        <v>19.195</v>
+        <v>0</v>
       </c>
       <c r="M133" s="22" t="n">
-        <v>20.545</v>
-      </c>
-      <c r="S133" s="22" t="n">
+        <v>-60.158</v>
+      </c>
+      <c r="W133" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="22" t="n">
-        <v>14.129</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>19.563</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>19.346</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>19.195</v>
-      </c>
       <c r="X133" s="22" t="n">
-        <v>20.545</v>
+        <v>-60.158</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-25.727</v>
+        <v>-53.362</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>-37.706</v>
+        <v>-34.709</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>-41.975</v>
-      </c>
-      <c r="O134" s="22" t="n">
-        <v>-8.608000000000001</v>
-      </c>
-      <c r="P134" s="22" t="n">
-        <v>-9.09</v>
-      </c>
-      <c r="Q134" s="22" t="n">
-        <v>-11.783</v>
-      </c>
-      <c r="R134" s="22" t="n">
-        <v>-9.694000000000001</v>
-      </c>
-      <c r="S134" s="22" t="n">
-        <v>-8.034000000000001</v>
-      </c>
-      <c r="T134" s="22" t="n">
-        <v>-12.793</v>
+        <v>-11.679</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>-16.414</v>
+        <v>0</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>-25.727</v>
+        <v>-53.362</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>-37.706</v>
+        <v>-34.709</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>-41.975</v>
+        <v>-11.679</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>보험금 수익</t>
         </is>
       </c>
       <c r="E135" s="22" t="n">
-        <v>13.067</v>
+        <v>-1.015</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>41.234</v>
+        <v>-1.629</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>53.611</v>
+        <v>-16.604</v>
       </c>
       <c r="O135" s="22" t="n">
-        <v>28.768</v>
+        <v>-11.858</v>
       </c>
       <c r="P135" s="22" t="n">
-        <v>38.523</v>
+        <v>-170.867</v>
       </c>
       <c r="Q135" s="22" t="n">
-        <v>31.747</v>
+        <v>-14.268</v>
       </c>
       <c r="R135" s="22" t="n">
-        <v>8.964</v>
+        <v>-15.099</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>5.522</v>
+        <v>-12.122</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>3.677</v>
+        <v>-4.298</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>5.517</v>
+        <v>-0.075</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>13.067</v>
+        <v>-1.015</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>41.234</v>
+        <v>-1.629</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>53.611</v>
+        <v>-16.604</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="E136" s="22" t="n">
-        <v>-72.61799999999999</v>
-      </c>
-      <c r="I136" s="22" t="n">
-        <v>33.734</v>
-      </c>
-      <c r="M136" s="22" t="n">
-        <v>-2.288</v>
+          <t>대손충당금 증감</t>
+        </is>
       </c>
       <c r="O136" s="22" t="n">
-        <v>137.435</v>
+        <v>28.824</v>
       </c>
       <c r="P136" s="22" t="n">
-        <v>50.363</v>
+        <v>-6.781</v>
       </c>
       <c r="Q136" s="22" t="n">
-        <v>119.002</v>
+        <v>0.92</v>
       </c>
       <c r="R136" s="22" t="n">
-        <v>7.908</v>
-      </c>
-      <c r="S136" s="22" t="n">
-        <v>28.627</v>
-      </c>
-      <c r="T136" s="22" t="n">
-        <v>-34.503</v>
-      </c>
-      <c r="U136" s="22" t="n">
-        <v>-69.79900000000001</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>-72.61799999999999</v>
-      </c>
-      <c r="W136" s="22" t="n">
-        <v>33.734</v>
-      </c>
-      <c r="X136" s="22" t="n">
-        <v>-2.288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>유형자산 제각손실</t>
+          <t>퇴직급여자산 증감</t>
         </is>
       </c>
       <c r="E137" s="22" t="n">
-        <v>44.129</v>
+        <v>0</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>4.89</v>
+        <v>-80.547</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>6.824</v>
-      </c>
-      <c r="O137" s="22" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="P137" s="22" t="n">
-        <v>29.908</v>
-      </c>
-      <c r="Q137" s="22" t="n">
-        <v>14.141</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>22.024</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>67.898</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>66.256</v>
+        <v>-104.594</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>44.129</v>
+        <v>0</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>4.89</v>
+        <v>-80.547</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>6.824</v>
+        <v>-104.594</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>무형자산 제각손실</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="E138" s="22" t="n">
-        <v>2.04</v>
+        <v>-70.854</v>
       </c>
       <c r="I138" s="22" t="n">
+        <v>-67.399</v>
+      </c>
+      <c r="M138" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="O138" s="22" t="n">
+        <v>61.438</v>
+      </c>
+      <c r="P138" s="22" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="Q138" s="22" t="n">
+        <v>14.004</v>
+      </c>
+      <c r="R138" s="22" t="n">
+        <v>-0.979</v>
+      </c>
+      <c r="S138" s="22" t="n">
+        <v>19.076</v>
+      </c>
+      <c r="T138" s="22" t="n">
+        <v>-683.3869999999999</v>
+      </c>
       <c r="U138" s="22" t="n">
-        <v>0</v>
+        <v>-197.694</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>2.04</v>
+        <v>-70.854</v>
       </c>
       <c r="W138" s="22" t="n">
+        <v>-67.399</v>
+      </c>
+      <c r="X138" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>투자유가증권 평가손익</t>
         </is>
       </c>
       <c r="E139" s="22" t="n">
-        <v>-615.729</v>
+        <v>0</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>739.549</v>
+        <v>7.729</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-834.127</v>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>-893.998</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>-1248.622</v>
-      </c>
-      <c r="Q139" s="22" t="n">
-        <v>587.679</v>
-      </c>
-      <c r="R139" s="22" t="n">
-        <v>-274.998</v>
-      </c>
-      <c r="S139" s="22" t="n">
-        <v>-665.6180000000001</v>
-      </c>
-      <c r="T139" s="22" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="U139" s="22" t="n">
-        <v>455.724</v>
+        <v>0</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>-615.729</v>
+        <v>0</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>739.549</v>
+        <v>7.729</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-834.127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-171.306</v>
+        <v>19.346</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>374.138</v>
+        <v>19.195</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>157.394</v>
-      </c>
-      <c r="O140" s="22" t="n">
-        <v>40.984</v>
-      </c>
-      <c r="P140" s="22" t="n">
-        <v>-456.775</v>
-      </c>
-      <c r="Q140" s="22" t="n">
-        <v>-893.146</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>54.636</v>
+        <v>20.545</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>365.915</v>
+        <v>0</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>-807.812</v>
+        <v>14.129</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>-2358.021</v>
+        <v>19.563</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-171.306</v>
+        <v>19.346</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>374.138</v>
+        <v>19.195</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>157.394</v>
+        <v>20.545</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="E141" s="22" t="n">
-        <v>245.894</v>
+        <v>-25.727</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>207.979</v>
+        <v>-37.706</v>
       </c>
       <c r="M141" s="22" t="n">
-        <v>150.185</v>
+        <v>-41.975</v>
       </c>
       <c r="O141" s="22" t="n">
-        <v>-18.786</v>
+        <v>-8.608000000000001</v>
       </c>
       <c r="P141" s="22" t="n">
-        <v>89.093</v>
+        <v>-9.09</v>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>-208.055</v>
+        <v>-11.783</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>124.051</v>
+        <v>-9.694000000000001</v>
       </c>
       <c r="S141" s="22" t="n">
-        <v>-46.497</v>
+        <v>-8.034000000000001</v>
       </c>
       <c r="T141" s="22" t="n">
-        <v>-206.966</v>
+        <v>-12.793</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>-444.539</v>
+        <v>-16.414</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>245.894</v>
+        <v>-25.727</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>207.979</v>
+        <v>-37.706</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>150.185</v>
+        <v>-41.975</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E142" s="22" t="n">
-        <v>42.01</v>
+        <v>13.067</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>-87.489</v>
+        <v>41.234</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>381.101</v>
+        <v>53.611</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>173.23</v>
+        <v>28.768</v>
       </c>
       <c r="P142" s="22" t="n">
-        <v>262.815</v>
+        <v>38.523</v>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>-29.757</v>
+        <v>31.747</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>-113.356</v>
+        <v>8.964</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-607.669</v>
+        <v>5.522</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>136.088</v>
+        <v>3.677</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>-60.019</v>
+        <v>5.517</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>42.01</v>
+        <v>13.067</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-87.489</v>
+        <v>41.234</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>381.101</v>
+        <v>53.611</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>미수 소비세 증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="E143" s="22" t="n">
-        <v>0</v>
+        <v>-72.61799999999999</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>-779.073</v>
+        <v>33.734</v>
       </c>
       <c r="M143" s="22" t="n">
-        <v>779.073</v>
+        <v>-2.288</v>
+      </c>
+      <c r="O143" s="22" t="n">
+        <v>137.435</v>
+      </c>
+      <c r="P143" s="22" t="n">
+        <v>50.363</v>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>119.002</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>7.908</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>28.627</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>-34.503</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>-69.79900000000001</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>0</v>
+        <v>-72.61799999999999</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>-779.073</v>
+        <v>33.734</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>779.073</v>
+        <v>-2.288</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
+          <t>유형자산 제각손실</t>
         </is>
       </c>
       <c r="E144" s="22" t="n">
-        <v>143.809</v>
+        <v>44.129</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-116.509</v>
+        <v>4.89</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>394.094</v>
+        <v>6.824</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>140.279</v>
+        <v>19.34</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-83.917</v>
+        <v>29.908</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>-48.709</v>
+        <v>14.141</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>119.962</v>
+        <v>22.024</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>-39.894</v>
+        <v>27.72</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-57.342</v>
+        <v>67.898</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>-21.121</v>
+        <v>66.256</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>143.809</v>
+        <v>44.129</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-116.509</v>
+        <v>4.89</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>394.094</v>
+        <v>6.824</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
+          <t>무형자산 제각손실</t>
         </is>
       </c>
       <c r="E145" s="22" t="n">
-        <v>-321.817</v>
+        <v>2.04</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>231.957</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>-85.40300000000001</v>
-      </c>
-      <c r="O145" s="22" t="n">
-        <v>191.277</v>
-      </c>
-      <c r="P145" s="22" t="n">
-        <v>272.203</v>
-      </c>
-      <c r="Q145" s="22" t="n">
-        <v>-254.95</v>
-      </c>
-      <c r="R145" s="22" t="n">
-        <v>-25.149</v>
-      </c>
-      <c r="S145" s="22" t="n">
-        <v>243.592</v>
-      </c>
-      <c r="T145" s="22" t="n">
-        <v>-169.731</v>
+        <v>0</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>-196.154</v>
+        <v>0</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>-321.817</v>
+        <v>2.04</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>231.957</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>-85.40300000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="E146" s="22" t="n">
-        <v>49.141</v>
+        <v>-615.729</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>27.432</v>
+        <v>739.549</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>34.877</v>
+        <v>-834.127</v>
       </c>
       <c r="O146" s="22" t="n">
-        <v>179.186</v>
+        <v>-893.998</v>
       </c>
       <c r="P146" s="22" t="n">
-        <v>90.203</v>
+        <v>-1248.622</v>
       </c>
       <c r="Q146" s="22" t="n">
-        <v>208.406</v>
+        <v>587.679</v>
       </c>
       <c r="R146" s="22" t="n">
-        <v>78.03400000000001</v>
+        <v>-274.998</v>
       </c>
       <c r="S146" s="22" t="n">
-        <v>84.477</v>
+        <v>-665.6180000000001</v>
       </c>
       <c r="T146" s="22" t="n">
-        <v>63.905</v>
+        <v>84.5</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>85.66200000000001</v>
+        <v>455.724</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>49.141</v>
+        <v>-615.729</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>27.432</v>
+        <v>739.549</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>34.877</v>
+        <v>-834.127</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="E147" s="22" t="n">
-        <v>2675.246</v>
+        <v>-171.306</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>3950.98</v>
+        <v>374.138</v>
       </c>
       <c r="M147" s="22" t="n">
-        <v>5949.902</v>
+        <v>157.394</v>
       </c>
       <c r="O147" s="22" t="n">
-        <v>2037.508</v>
+        <v>40.984</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>1972.134</v>
+        <v>-456.775</v>
       </c>
       <c r="Q147" s="22" t="n">
-        <v>2022.872</v>
+        <v>-893.146</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>2201.797</v>
+        <v>54.636</v>
       </c>
       <c r="S147" s="22" t="n">
-        <v>3470.545</v>
+        <v>365.915</v>
       </c>
       <c r="T147" s="22" t="n">
-        <v>3986.046</v>
+        <v>-807.812</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>2211.322</v>
+        <v>-2358.021</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>2675.246</v>
+        <v>-171.306</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>3950.98</v>
+        <v>374.138</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>5949.902</v>
+        <v>157.394</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>기타 자산 증감</t>
         </is>
       </c>
       <c r="E148" s="22" t="n">
-        <v>25.727</v>
+        <v>245.894</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>37.706</v>
+        <v>207.979</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>41.975</v>
+        <v>150.185</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>8.519</v>
+        <v>-18.786</v>
       </c>
       <c r="P148" s="22" t="n">
-        <v>8.816000000000001</v>
+        <v>89.093</v>
       </c>
       <c r="Q148" s="22" t="n">
-        <v>11.783</v>
+        <v>-208.055</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>9.694000000000001</v>
+        <v>124.051</v>
       </c>
       <c r="S148" s="22" t="n">
-        <v>8.034000000000001</v>
+        <v>-46.497</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>12.793</v>
+        <v>-206.966</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>16.414</v>
+        <v>-444.539</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>25.727</v>
+        <v>245.894</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>37.706</v>
+        <v>207.979</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>41.975</v>
+        <v>150.185</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="E149" s="22" t="n">
-        <v>-12.701</v>
+        <v>42.01</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>-41.177</v>
+        <v>-87.489</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>-52.157</v>
+        <v>381.101</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>-28.289</v>
+        <v>173.23</v>
       </c>
       <c r="P149" s="22" t="n">
-        <v>-37.51</v>
+        <v>262.815</v>
       </c>
       <c r="Q149" s="22" t="n">
-        <v>-35.105</v>
+        <v>-29.757</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>-8.962999999999999</v>
+        <v>-113.356</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>-5.488</v>
+        <v>-607.669</v>
       </c>
       <c r="T149" s="22" t="n">
-        <v>-3.71</v>
+        <v>136.088</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>-5.333</v>
+        <v>-60.019</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>-12.701</v>
+        <v>42.01</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>-41.177</v>
+        <v>-87.489</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>-52.157</v>
+        <v>381.101</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
-        </is>
+          <t>미수 소비세 증감</t>
+        </is>
+      </c>
+      <c r="E150" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="I150" s="22" t="n">
+        <v>-779.073</v>
+      </c>
+      <c r="M150" s="22" t="n">
+        <v>779.073</v>
+      </c>
+      <c r="V150" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M150" s="22" t="n">
-        <v>60.158</v>
-      </c>
       <c r="W150" s="22" t="n">
-        <v>0</v>
+        <v>-779.073</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>60.158</v>
+        <v>779.073</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="E151" s="22" t="n">
-        <v>53.362</v>
+        <v>143.809</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>34.709</v>
+        <v>-116.509</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>11.679</v>
+        <v>394.094</v>
+      </c>
+      <c r="O151" s="22" t="n">
+        <v>140.279</v>
+      </c>
+      <c r="P151" s="22" t="n">
+        <v>-83.917</v>
+      </c>
+      <c r="Q151" s="22" t="n">
+        <v>-48.709</v>
+      </c>
+      <c r="R151" s="22" t="n">
+        <v>119.962</v>
+      </c>
+      <c r="S151" s="22" t="n">
+        <v>-39.894</v>
+      </c>
+      <c r="T151" s="22" t="n">
+        <v>-57.342</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>0</v>
+        <v>-21.121</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>53.362</v>
+        <v>143.809</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>34.709</v>
+        <v>-116.509</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>11.679</v>
+        <v>394.094</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
+          <t>기타 부채 증감</t>
         </is>
       </c>
       <c r="E152" s="22" t="n">
-        <v>0.777</v>
+        <v>-321.817</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>1.6</v>
+        <v>231.957</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>11.531</v>
+        <v>-85.40300000000001</v>
       </c>
       <c r="O152" s="22" t="n">
-        <v>63.921</v>
+        <v>191.277</v>
       </c>
       <c r="P152" s="22" t="n">
-        <v>144.935</v>
+        <v>272.203</v>
       </c>
       <c r="Q152" s="22" t="n">
-        <v>32.527</v>
+        <v>-254.95</v>
       </c>
       <c r="R152" s="22" t="n">
-        <v>26.424</v>
+        <v>-25.149</v>
       </c>
       <c r="S152" s="22" t="n">
-        <v>14.597</v>
+        <v>243.592</v>
       </c>
       <c r="T152" s="22" t="n">
-        <v>4.4</v>
+        <v>-169.731</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>0</v>
+        <v>-196.154</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>0.777</v>
+        <v>-321.817</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>1.6</v>
+        <v>231.957</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>11.531</v>
+        <v>-85.40300000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E153" s="22" t="n">
-        <v>-845.734</v>
+        <v>49.141</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-251.009</v>
+        <v>27.432</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>-813.018</v>
+        <v>34.877</v>
       </c>
       <c r="O153" s="22" t="n">
-        <v>-28.686</v>
+        <v>179.186</v>
       </c>
       <c r="P153" s="22" t="n">
-        <v>-320.458</v>
+        <v>90.203</v>
       </c>
       <c r="Q153" s="22" t="n">
-        <v>-614.9450000000001</v>
+        <v>208.406</v>
       </c>
       <c r="R153" s="22" t="n">
-        <v>-28.916</v>
+        <v>78.03400000000001</v>
       </c>
       <c r="S153" s="22" t="n">
-        <v>-268.439</v>
+        <v>84.477</v>
       </c>
       <c r="T153" s="22" t="n">
-        <v>-1091.748</v>
+        <v>63.905</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>-1537.092</v>
+        <v>85.66200000000001</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>-845.734</v>
+        <v>49.141</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-251.009</v>
+        <v>27.432</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>-813.018</v>
+        <v>34.877</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="E154" s="22" t="n">
-        <v>13.604</v>
+        <v>2675.246</v>
       </c>
       <c r="I154" s="22" t="n">
-        <v>68.205</v>
+        <v>3950.98</v>
       </c>
       <c r="M154" s="22" t="n">
-        <v>30.38</v>
+        <v>5949.902</v>
       </c>
       <c r="O154" s="22" t="n">
-        <v>74.607</v>
+        <v>2037.508</v>
       </c>
       <c r="P154" s="22" t="n">
-        <v>0</v>
+        <v>1972.134</v>
       </c>
       <c r="Q154" s="22" t="n">
-        <v>0.452</v>
+        <v>2022.872</v>
       </c>
       <c r="R154" s="22" t="n">
-        <v>238.91</v>
+        <v>2201.797</v>
       </c>
       <c r="S154" s="22" t="n">
-        <v>0</v>
+        <v>3470.545</v>
+      </c>
+      <c r="T154" s="22" t="n">
+        <v>3986.046</v>
       </c>
       <c r="U154" s="22" t="n">
-        <v>0</v>
+        <v>2211.322</v>
       </c>
       <c r="V154" s="22" t="n">
-        <v>13.604</v>
+        <v>2675.246</v>
       </c>
       <c r="W154" s="22" t="n">
-        <v>68.205</v>
+        <v>3950.98</v>
       </c>
       <c r="X154" s="22" t="n">
-        <v>30.38</v>
+        <v>5949.902</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>1910.284</v>
-      </c>
-      <c r="I155" s="12" t="n">
-        <v>3801.015</v>
-      </c>
-      <c r="M155" s="12" t="n">
-        <v>5240.452</v>
-      </c>
-      <c r="O155" s="12" t="n">
-        <v>2127.581</v>
-      </c>
-      <c r="P155" s="12" t="n">
-        <v>1767.917</v>
-      </c>
-      <c r="Q155" s="12" t="n">
-        <v>1417.583</v>
-      </c>
-      <c r="R155" s="12" t="n">
-        <v>2438.946</v>
-      </c>
-      <c r="S155" s="12" t="n">
-        <v>3219.249</v>
-      </c>
-      <c r="T155" s="12" t="n">
-        <v>2907.781</v>
-      </c>
-      <c r="U155" s="12" t="n">
-        <v>685.311</v>
-      </c>
-      <c r="V155" s="12" t="n">
-        <v>1910.284</v>
-      </c>
-      <c r="W155" s="12" t="n">
-        <v>3801.015</v>
-      </c>
-      <c r="X155" s="12" t="n">
-        <v>5240.452</v>
+      <c r="A155" s="20" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="n">
+        <v>25.727</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>37.706</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>41.975</v>
+      </c>
+      <c r="O155" s="22" t="n">
+        <v>8.519</v>
+      </c>
+      <c r="P155" s="22" t="n">
+        <v>8.816000000000001</v>
+      </c>
+      <c r="Q155" s="22" t="n">
+        <v>11.783</v>
+      </c>
+      <c r="R155" s="22" t="n">
+        <v>9.694000000000001</v>
+      </c>
+      <c r="S155" s="22" t="n">
+        <v>8.034000000000001</v>
+      </c>
+      <c r="T155" s="22" t="n">
+        <v>12.793</v>
+      </c>
+      <c r="U155" s="22" t="n">
+        <v>16.414</v>
+      </c>
+      <c r="V155" s="22" t="n">
+        <v>25.727</v>
+      </c>
+      <c r="W155" s="22" t="n">
+        <v>37.706</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>41.975</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>정기예금 순증감</t>
-        </is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="E156" s="22" t="n">
+        <v>-12.701</v>
+      </c>
+      <c r="I156" s="22" t="n">
+        <v>-41.177</v>
+      </c>
+      <c r="M156" s="22" t="n">
+        <v>-52.157</v>
+      </c>
+      <c r="O156" s="22" t="n">
+        <v>-28.289</v>
+      </c>
+      <c r="P156" s="22" t="n">
+        <v>-37.51</v>
+      </c>
+      <c r="Q156" s="22" t="n">
+        <v>-35.105</v>
       </c>
       <c r="R156" s="22" t="n">
-        <v>0</v>
+        <v>-8.962999999999999</v>
       </c>
       <c r="S156" s="22" t="n">
-        <v>-38.175</v>
+        <v>-5.488</v>
       </c>
       <c r="T156" s="22" t="n">
-        <v>38.175</v>
+        <v>-3.71</v>
       </c>
       <c r="U156" s="22" t="n">
-        <v>0</v>
+        <v>-5.333</v>
+      </c>
+      <c r="V156" s="22" t="n">
+        <v>-12.701</v>
+      </c>
+      <c r="W156" s="22" t="n">
+        <v>-41.177</v>
+      </c>
+      <c r="X156" s="22" t="n">
+        <v>-52.157</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="E157" s="22" t="n">
-        <v>-3386.895</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="I157" s="22" t="n">
-        <v>-5943.993</v>
+        <v>0</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>-1495.547</v>
-      </c>
-      <c r="O157" s="22" t="n">
-        <v>-742.11</v>
-      </c>
-      <c r="P157" s="22" t="n">
-        <v>-486.372</v>
-      </c>
-      <c r="Q157" s="22" t="n">
-        <v>-1009.038</v>
-      </c>
-      <c r="R157" s="22" t="n">
-        <v>-1032.146</v>
-      </c>
-      <c r="S157" s="22" t="n">
-        <v>-884.828</v>
-      </c>
-      <c r="T157" s="22" t="n">
-        <v>-1822.383</v>
-      </c>
-      <c r="U157" s="22" t="n">
-        <v>-3543.094</v>
-      </c>
-      <c r="V157" s="22" t="n">
-        <v>-3386.895</v>
+        <v>60.158</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>-5943.993</v>
+        <v>0</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>-1495.547</v>
+        <v>60.158</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Subsidy Inv CF</t>
-        </is>
-      </c>
-      <c r="O158" s="22" t="n">
-        <v>47.771</v>
-      </c>
-      <c r="P158" s="22" t="n">
+          <t>보조금 수취</t>
+        </is>
+      </c>
+      <c r="E158" s="22" t="n">
+        <v>53.362</v>
+      </c>
+      <c r="I158" s="22" t="n">
+        <v>34.709</v>
+      </c>
+      <c r="M158" s="22" t="n">
+        <v>11.679</v>
+      </c>
+      <c r="U158" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="V158" s="22" t="n">
+        <v>53.362</v>
+      </c>
+      <c r="W158" s="22" t="n">
+        <v>34.709</v>
+      </c>
+      <c r="X158" s="22" t="n">
+        <v>11.679</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Subsidy Etc Inv CF</t>
+          <t>보험금 수취</t>
         </is>
       </c>
       <c r="E159" s="22" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="I159" s="22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M159" s="22" t="n">
+        <v>11.531</v>
+      </c>
+      <c r="O159" s="22" t="n">
+        <v>63.921</v>
+      </c>
+      <c r="P159" s="22" t="n">
+        <v>144.935</v>
+      </c>
+      <c r="Q159" s="22" t="n">
+        <v>32.527</v>
+      </c>
+      <c r="R159" s="22" t="n">
+        <v>26.424</v>
+      </c>
+      <c r="S159" s="22" t="n">
+        <v>14.597</v>
+      </c>
+      <c r="T159" s="22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U159" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I159" s="22" t="n">
-        <v>2622.486</v>
-      </c>
-      <c r="M159" s="22" t="n">
-        <v>294.115</v>
-      </c>
-      <c r="P159" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q159" s="22" t="n">
-        <v>1.788</v>
-      </c>
-      <c r="R159" s="22" t="n">
-        <v>1.575</v>
-      </c>
-      <c r="S159" s="22" t="n">
-        <v>3.359</v>
-      </c>
-      <c r="T159" s="22" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="U159" s="22" t="n">
-        <v>17.345</v>
-      </c>
       <c r="V159" s="22" t="n">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>2622.486</v>
+        <v>1.6</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>294.115</v>
+        <v>11.531</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-20.089</v>
+        <v>-845.734</v>
       </c>
       <c r="I160" s="22" t="n">
-        <v>-24.597</v>
+        <v>-251.009</v>
       </c>
       <c r="M160" s="22" t="n">
-        <v>-131.606</v>
+        <v>-813.018</v>
       </c>
       <c r="O160" s="22" t="n">
-        <v>-5.797</v>
+        <v>-28.686</v>
       </c>
       <c r="P160" s="22" t="n">
-        <v>-1.529</v>
+        <v>-320.458</v>
       </c>
       <c r="Q160" s="22" t="n">
-        <v>-47.817</v>
+        <v>-614.9450000000001</v>
       </c>
       <c r="R160" s="22" t="n">
-        <v>-3.875</v>
+        <v>-28.916</v>
       </c>
       <c r="S160" s="22" t="n">
-        <v>-13.2</v>
+        <v>-268.439</v>
       </c>
       <c r="T160" s="22" t="n">
-        <v>-70.04900000000001</v>
+        <v>-1091.748</v>
       </c>
       <c r="U160" s="22" t="n">
-        <v>-26.054</v>
+        <v>-1537.092</v>
       </c>
       <c r="V160" s="22" t="n">
-        <v>-20.089</v>
+        <v>-845.734</v>
       </c>
       <c r="W160" s="22" t="n">
-        <v>-24.597</v>
+        <v>-251.009</v>
       </c>
       <c r="X160" s="22" t="n">
-        <v>-131.606</v>
+        <v>-813.018</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>법인세 환급</t>
         </is>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-0.907</v>
+        <v>13.604</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>-0.984</v>
+        <v>68.205</v>
       </c>
       <c r="M161" s="22" t="n">
-        <v>-1.069</v>
+        <v>30.38</v>
       </c>
       <c r="O161" s="22" t="n">
-        <v>-0.498</v>
+        <v>74.607</v>
       </c>
       <c r="P161" s="22" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q161" s="22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.452</v>
       </c>
       <c r="R161" s="22" t="n">
-        <v>-0.63</v>
+        <v>238.91</v>
       </c>
       <c r="S161" s="22" t="n">
-        <v>-0.643</v>
-      </c>
-      <c r="T161" s="22" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>-0.779</v>
+        <v>0</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>-0.907</v>
+        <v>13.604</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>-0.984</v>
+        <v>68.205</v>
       </c>
       <c r="X161" s="22" t="n">
-        <v>-1.069</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각</t>
-        </is>
-      </c>
-      <c r="O162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" s="22" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q162" s="22" t="n">
-        <v>0</v>
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="n">
+        <v>1910.284</v>
+      </c>
+      <c r="I162" s="12" t="n">
+        <v>3801.015</v>
+      </c>
+      <c r="M162" s="12" t="n">
+        <v>5240.452</v>
+      </c>
+      <c r="O162" s="12" t="n">
+        <v>2127.581</v>
+      </c>
+      <c r="P162" s="12" t="n">
+        <v>1767.917</v>
+      </c>
+      <c r="Q162" s="12" t="n">
+        <v>1417.583</v>
+      </c>
+      <c r="R162" s="12" t="n">
+        <v>2438.946</v>
+      </c>
+      <c r="S162" s="12" t="n">
+        <v>3219.249</v>
+      </c>
+      <c r="T162" s="12" t="n">
+        <v>2907.781</v>
+      </c>
+      <c r="U162" s="12" t="n">
+        <v>685.311</v>
+      </c>
+      <c r="V162" s="12" t="n">
+        <v>1910.284</v>
+      </c>
+      <c r="W162" s="12" t="n">
+        <v>3801.015</v>
+      </c>
+      <c r="X162" s="12" t="n">
+        <v>5240.452</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
-      </c>
-      <c r="O163" s="22" t="n">
-        <v>-99.379</v>
-      </c>
-      <c r="P163" s="22" t="n">
+          <t>정기예금 순증감</t>
+        </is>
+      </c>
+      <c r="R163" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="22" t="n">
+        <v>-38.175</v>
+      </c>
+      <c r="T163" s="22" t="n">
+        <v>38.175</v>
+      </c>
+      <c r="U163" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Liquidation Of Subsidiaries And Associates Resulting In Change In Scope Of Consolidation Inv CF</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E164" s="22" t="n">
+        <v>-3386.895</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>-5943.993</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>-1495.547</v>
+      </c>
+      <c r="O164" s="22" t="n">
+        <v>-742.11</v>
       </c>
       <c r="P164" s="22" t="n">
-        <v>0</v>
+        <v>-486.372</v>
       </c>
       <c r="Q164" s="22" t="n">
-        <v>578.659</v>
+        <v>-1009.038</v>
       </c>
       <c r="R164" s="22" t="n">
-        <v>0</v>
+        <v>-1032.146</v>
+      </c>
+      <c r="S164" s="22" t="n">
+        <v>-884.828</v>
+      </c>
+      <c r="T164" s="22" t="n">
+        <v>-1822.383</v>
+      </c>
+      <c r="U164" s="22" t="n">
+        <v>-3543.094</v>
+      </c>
+      <c r="V164" s="22" t="n">
+        <v>-3386.895</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>-5943.993</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>-1495.547</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E165" s="22" t="n">
-        <v>-4.513</v>
-      </c>
-      <c r="I165" s="22" t="n">
-        <v>-54.619</v>
-      </c>
-      <c r="M165" s="22" t="n">
-        <v>-63.309</v>
+          <t>Proceeds From Subsidy Inv CF</t>
+        </is>
       </c>
       <c r="O165" s="22" t="n">
-        <v>-38.101</v>
+        <v>47.771</v>
       </c>
       <c r="P165" s="22" t="n">
-        <v>-29.244</v>
-      </c>
-      <c r="Q165" s="22" t="n">
-        <v>-47.766</v>
-      </c>
-      <c r="R165" s="22" t="n">
-        <v>-25.084</v>
-      </c>
-      <c r="S165" s="22" t="n">
-        <v>-55.283</v>
-      </c>
-      <c r="T165" s="22" t="n">
-        <v>-13.071</v>
-      </c>
-      <c r="U165" s="22" t="n">
-        <v>-47.013</v>
-      </c>
-      <c r="V165" s="22" t="n">
-        <v>-4.513</v>
-      </c>
-      <c r="W165" s="22" t="n">
-        <v>-54.619</v>
-      </c>
-      <c r="X165" s="22" t="n">
-        <v>-63.309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E166" s="12" t="n">
-        <v>-3412.406</v>
-      </c>
-      <c r="I166" s="12" t="n">
-        <v>-3401.708</v>
-      </c>
-      <c r="M166" s="12" t="n">
-        <v>-1397.418</v>
-      </c>
-      <c r="O166" s="12" t="n">
-        <v>-838.115</v>
-      </c>
-      <c r="P166" s="12" t="n">
-        <v>-517.701</v>
-      </c>
-      <c r="Q166" s="12" t="n">
-        <v>-524.739</v>
-      </c>
-      <c r="R166" s="12" t="n">
-        <v>-1060.159</v>
-      </c>
-      <c r="S166" s="12" t="n">
-        <v>-988.771</v>
-      </c>
-      <c r="T166" s="12" t="n">
-        <v>-1837.499</v>
-      </c>
-      <c r="U166" s="12" t="n">
-        <v>-3599.596</v>
-      </c>
-      <c r="V166" s="12" t="n">
-        <v>-3412.406</v>
-      </c>
-      <c r="W166" s="12" t="n">
-        <v>-3401.708</v>
-      </c>
-      <c r="X166" s="12" t="n">
-        <v>-1397.418</v>
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Subsidy Etc Inv CF</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="22" t="n">
+        <v>2622.486</v>
+      </c>
+      <c r="M166" s="22" t="n">
+        <v>294.115</v>
+      </c>
+      <c r="P166" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="22" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="R166" s="22" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="S166" s="22" t="n">
+        <v>3.359</v>
+      </c>
+      <c r="T166" s="22" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="U166" s="22" t="n">
+        <v>17.345</v>
+      </c>
+      <c r="V166" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="22" t="n">
+        <v>2622.486</v>
+      </c>
+      <c r="X166" s="22" t="n">
+        <v>294.115</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="E167" s="22" t="n">
-        <v>0</v>
+        <v>-20.089</v>
       </c>
       <c r="I167" s="22" t="n">
-        <v>1500</v>
+        <v>-24.597</v>
       </c>
       <c r="M167" s="22" t="n">
-        <v>-1500</v>
+        <v>-131.606</v>
       </c>
       <c r="O167" s="22" t="n">
-        <v>-450.181</v>
+        <v>-5.797</v>
       </c>
       <c r="P167" s="22" t="n">
-        <v>130.87</v>
+        <v>-1.529</v>
       </c>
       <c r="Q167" s="22" t="n">
-        <v>-500.832</v>
+        <v>-47.817</v>
       </c>
       <c r="R167" s="22" t="n">
-        <v>-460.598</v>
+        <v>-3.875</v>
       </c>
       <c r="S167" s="22" t="n">
-        <v>61.757</v>
+        <v>-13.2</v>
       </c>
       <c r="T167" s="22" t="n">
-        <v>0</v>
+        <v>-70.04900000000001</v>
       </c>
       <c r="U167" s="22" t="n">
-        <v>-600</v>
+        <v>-26.054</v>
       </c>
       <c r="V167" s="22" t="n">
-        <v>0</v>
+        <v>-20.089</v>
       </c>
       <c r="W167" s="22" t="n">
-        <v>1500</v>
+        <v>-24.597</v>
       </c>
       <c r="X167" s="22" t="n">
-        <v>-1500</v>
+        <v>-131.606</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="E168" s="22" t="n">
-        <v>4300</v>
+        <v>-0.907</v>
       </c>
       <c r="I168" s="22" t="n">
-        <v>1000</v>
+        <v>-0.984</v>
       </c>
       <c r="M168" s="22" t="n">
-        <v>1500</v>
+        <v>-1.069</v>
       </c>
       <c r="O168" s="22" t="n">
-        <v>2000</v>
+        <v>-0.498</v>
       </c>
       <c r="P168" s="22" t="n">
-        <v>0</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="Q168" s="22" t="n">
-        <v>1000</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="R168" s="22" t="n">
-        <v>1200</v>
+        <v>-0.63</v>
       </c>
       <c r="S168" s="22" t="n">
-        <v>2000</v>
+        <v>-0.643</v>
       </c>
       <c r="T168" s="22" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="U168" s="22" t="n">
-        <v>4700</v>
+        <v>-0.779</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>4300</v>
+        <v>-0.907</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>1000</v>
+        <v>-0.984</v>
       </c>
       <c r="X168" s="22" t="n">
-        <v>1500</v>
+        <v>-1.069</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="E169" s="22" t="n">
-        <v>-1856.779</v>
-      </c>
-      <c r="I169" s="22" t="n">
-        <v>-2406.56</v>
-      </c>
-      <c r="M169" s="22" t="n">
-        <v>-2496.703</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="O169" s="22" t="n">
-        <v>-2379.506</v>
+        <v>0</v>
       </c>
       <c r="P169" s="22" t="n">
-        <v>-1505.004</v>
+        <v>0.003</v>
       </c>
       <c r="Q169" s="22" t="n">
-        <v>-1359.984</v>
-      </c>
-      <c r="R169" s="22" t="n">
-        <v>-1457.418</v>
-      </c>
-      <c r="S169" s="22" t="n">
-        <v>-1304.916</v>
-      </c>
-      <c r="T169" s="22" t="n">
-        <v>-964.9640000000001</v>
-      </c>
-      <c r="U169" s="22" t="n">
-        <v>-1201.579</v>
-      </c>
-      <c r="V169" s="22" t="n">
-        <v>-1856.779</v>
-      </c>
-      <c r="W169" s="22" t="n">
-        <v>-2406.56</v>
-      </c>
-      <c r="X169" s="22" t="n">
-        <v>-2496.703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>자기주식 처분</t>
+          <t>연결범위 변경 자회사 주식 취득</t>
         </is>
       </c>
       <c r="O170" s="22" t="n">
-        <v>0.013</v>
+        <v>-99.379</v>
       </c>
       <c r="P170" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" s="22" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="R170" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="E171" s="22" t="n">
-        <v>-301.909</v>
-      </c>
-      <c r="I171" s="22" t="n">
-        <v>-198.933</v>
-      </c>
-      <c r="M171" s="22" t="n">
-        <v>-0.231</v>
-      </c>
-      <c r="O171" s="22" t="n">
+          <t>Proceeds From Liquidation Of Subsidiaries And Associates Resulting In Change In Scope Of Consolidation Inv CF</t>
+        </is>
+      </c>
+      <c r="P171" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P171" s="22" t="n">
-        <v>-0.615</v>
-      </c>
       <c r="Q171" s="22" t="n">
-        <v>-0.226</v>
+        <v>578.659</v>
       </c>
       <c r="R171" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S171" s="22" t="n">
-        <v>-0.388</v>
-      </c>
-      <c r="T171" s="22" t="n">
-        <v>-0.277</v>
-      </c>
-      <c r="U171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V171" s="22" t="n">
-        <v>-301.909</v>
-      </c>
-      <c r="W171" s="22" t="n">
-        <v>-198.933</v>
-      </c>
-      <c r="X171" s="22" t="n">
-        <v>-0.231</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E172" s="22" t="n">
-        <v>-642.824</v>
+        <v>-4.513</v>
       </c>
       <c r="I172" s="22" t="n">
-        <v>-531.825</v>
+        <v>-54.619</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>-790.578</v>
+        <v>-63.309</v>
       </c>
       <c r="O172" s="22" t="n">
-        <v>-193.625</v>
+        <v>-38.101</v>
       </c>
       <c r="P172" s="22" t="n">
-        <v>-193.624</v>
+        <v>-29.244</v>
       </c>
       <c r="Q172" s="22" t="n">
-        <v>-204.377</v>
+        <v>-47.766</v>
       </c>
       <c r="R172" s="22" t="n">
-        <v>-215.133</v>
+        <v>-25.084</v>
       </c>
       <c r="S172" s="22" t="n">
-        <v>-215.133</v>
+        <v>-55.283</v>
       </c>
       <c r="T172" s="22" t="n">
-        <v>-290.503</v>
+        <v>-13.071</v>
       </c>
       <c r="U172" s="22" t="n">
-        <v>-323.003</v>
+        <v>-47.013</v>
       </c>
       <c r="V172" s="22" t="n">
-        <v>-642.824</v>
+        <v>-4.513</v>
       </c>
       <c r="W172" s="22" t="n">
-        <v>-531.825</v>
+        <v>-54.619</v>
       </c>
       <c r="X172" s="22" t="n">
-        <v>-790.578</v>
+        <v>-63.309</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="20" t="inlineStr">
-        <is>
-          <t>Additional Purchase Of Investments In Subsidiaries From Non Controlling Shareholders Fin CF</t>
-        </is>
-      </c>
-      <c r="O173" s="22" t="n">
-        <v>-0.359</v>
-      </c>
-      <c r="P173" s="22" t="n">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v>-3412.406</v>
+      </c>
+      <c r="I173" s="12" t="n">
+        <v>-3401.708</v>
+      </c>
+      <c r="M173" s="12" t="n">
+        <v>-1397.418</v>
+      </c>
+      <c r="O173" s="12" t="n">
+        <v>-838.115</v>
+      </c>
+      <c r="P173" s="12" t="n">
+        <v>-517.701</v>
+      </c>
+      <c r="Q173" s="12" t="n">
+        <v>-524.739</v>
+      </c>
+      <c r="R173" s="12" t="n">
+        <v>-1060.159</v>
+      </c>
+      <c r="S173" s="12" t="n">
+        <v>-988.771</v>
+      </c>
+      <c r="T173" s="12" t="n">
+        <v>-1837.499</v>
+      </c>
+      <c r="U173" s="12" t="n">
+        <v>-3599.596</v>
+      </c>
+      <c r="V173" s="12" t="n">
+        <v>-3412.406</v>
+      </c>
+      <c r="W173" s="12" t="n">
+        <v>-3401.708</v>
+      </c>
+      <c r="X173" s="12" t="n">
+        <v>-1397.418</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="20" t="inlineStr">
+        <is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="E174" s="22" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E174" s="12" t="n">
-        <v>1498.486</v>
-      </c>
-      <c r="I174" s="12" t="n">
-        <v>-637.318</v>
-      </c>
-      <c r="M174" s="12" t="n">
-        <v>-3287.513</v>
-      </c>
-      <c r="O174" s="12" t="n">
-        <v>-1023.659</v>
-      </c>
-      <c r="P174" s="12" t="n">
-        <v>-1568.373</v>
-      </c>
-      <c r="Q174" s="12" t="n">
-        <v>-1065.358</v>
-      </c>
-      <c r="R174" s="12" t="n">
-        <v>-933.15</v>
-      </c>
-      <c r="S174" s="12" t="n">
-        <v>541.319</v>
-      </c>
-      <c r="T174" s="12" t="n">
-        <v>-1255.745</v>
-      </c>
-      <c r="U174" s="12" t="n">
-        <v>2575.417</v>
-      </c>
-      <c r="V174" s="12" t="n">
-        <v>1498.486</v>
-      </c>
-      <c r="W174" s="12" t="n">
-        <v>-637.318</v>
-      </c>
-      <c r="X174" s="12" t="n">
-        <v>-3287.513</v>
+      <c r="I174" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M174" s="22" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="O174" s="22" t="n">
+        <v>-450.181</v>
+      </c>
+      <c r="P174" s="22" t="n">
+        <v>130.87</v>
+      </c>
+      <c r="Q174" s="22" t="n">
+        <v>-500.832</v>
+      </c>
+      <c r="R174" s="22" t="n">
+        <v>-460.598</v>
+      </c>
+      <c r="S174" s="22" t="n">
+        <v>61.757</v>
+      </c>
+      <c r="T174" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" s="22" t="n">
+        <v>-600</v>
+      </c>
+      <c r="V174" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="X174" s="22" t="n">
+        <v>-1500</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>장기차입</t>
         </is>
       </c>
       <c r="E175" s="22" t="n">
-        <v>86.271</v>
+        <v>4300</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>58.059</v>
+        <v>1000</v>
       </c>
       <c r="M175" s="22" t="n">
-        <v>59.61</v>
+        <v>1500</v>
       </c>
       <c r="O175" s="22" t="n">
-        <v>-48.272</v>
+        <v>2000</v>
       </c>
       <c r="P175" s="22" t="n">
-        <v>-19.457</v>
+        <v>0</v>
       </c>
       <c r="Q175" s="22" t="n">
-        <v>-24.537</v>
+        <v>1000</v>
       </c>
       <c r="R175" s="22" t="n">
-        <v>-8.282999999999999</v>
+        <v>1200</v>
       </c>
       <c r="S175" s="22" t="n">
-        <v>-23.911</v>
+        <v>2000</v>
       </c>
       <c r="T175" s="22" t="n">
-        <v>80.834</v>
+        <v>0</v>
       </c>
       <c r="U175" s="22" t="n">
-        <v>126.966</v>
+        <v>4700</v>
       </c>
       <c r="V175" s="22" t="n">
-        <v>86.271</v>
+        <v>4300</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>58.059</v>
+        <v>1000</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>59.61</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="E176" s="22" t="n">
+        <v>-1856.779</v>
+      </c>
+      <c r="I176" s="22" t="n">
+        <v>-2406.56</v>
+      </c>
+      <c r="M176" s="22" t="n">
+        <v>-2496.703</v>
+      </c>
+      <c r="O176" s="22" t="n">
+        <v>-2379.506</v>
+      </c>
+      <c r="P176" s="22" t="n">
+        <v>-1505.004</v>
+      </c>
+      <c r="Q176" s="22" t="n">
+        <v>-1359.984</v>
+      </c>
+      <c r="R176" s="22" t="n">
+        <v>-1457.418</v>
+      </c>
+      <c r="S176" s="22" t="n">
+        <v>-1304.916</v>
+      </c>
+      <c r="T176" s="22" t="n">
+        <v>-964.9640000000001</v>
+      </c>
+      <c r="U176" s="22" t="n">
+        <v>-1201.579</v>
+      </c>
+      <c r="V176" s="22" t="n">
+        <v>-1856.779</v>
+      </c>
+      <c r="W176" s="22" t="n">
+        <v>-2406.56</v>
+      </c>
+      <c r="X176" s="22" t="n">
+        <v>-2496.703</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 처분</t>
+        </is>
+      </c>
+      <c r="O177" s="22" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="P177" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="22" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="R177" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="n">
+        <v>-301.909</v>
+      </c>
+      <c r="I178" s="22" t="n">
+        <v>-198.933</v>
+      </c>
+      <c r="M178" s="22" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="O178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="22" t="n">
+        <v>-0.615</v>
+      </c>
+      <c r="Q178" s="22" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" s="22" t="n">
+        <v>-0.388</v>
+      </c>
+      <c r="T178" s="22" t="n">
+        <v>-0.277</v>
+      </c>
+      <c r="U178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>-301.909</v>
+      </c>
+      <c r="W178" s="22" t="n">
+        <v>-198.933</v>
+      </c>
+      <c r="X178" s="22" t="n">
+        <v>-0.231</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E179" s="22" t="n">
+        <v>-642.824</v>
+      </c>
+      <c r="I179" s="22" t="n">
+        <v>-531.825</v>
+      </c>
+      <c r="M179" s="22" t="n">
+        <v>-790.578</v>
+      </c>
+      <c r="O179" s="22" t="n">
+        <v>-193.625</v>
+      </c>
+      <c r="P179" s="22" t="n">
+        <v>-193.624</v>
+      </c>
+      <c r="Q179" s="22" t="n">
+        <v>-204.377</v>
+      </c>
+      <c r="R179" s="22" t="n">
+        <v>-215.133</v>
+      </c>
+      <c r="S179" s="22" t="n">
+        <v>-215.133</v>
+      </c>
+      <c r="T179" s="22" t="n">
+        <v>-290.503</v>
+      </c>
+      <c r="U179" s="22" t="n">
+        <v>-323.003</v>
+      </c>
+      <c r="V179" s="22" t="n">
+        <v>-642.824</v>
+      </c>
+      <c r="W179" s="22" t="n">
+        <v>-531.825</v>
+      </c>
+      <c r="X179" s="22" t="n">
+        <v>-790.578</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="20" t="inlineStr">
+        <is>
+          <t>Additional Purchase Of Investments In Subsidiaries From Non Controlling Shareholders Fin CF</t>
+        </is>
+      </c>
+      <c r="O180" s="22" t="n">
+        <v>-0.359</v>
+      </c>
+      <c r="P180" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v>1498.486</v>
+      </c>
+      <c r="I181" s="12" t="n">
+        <v>-637.318</v>
+      </c>
+      <c r="M181" s="12" t="n">
+        <v>-3287.513</v>
+      </c>
+      <c r="O181" s="12" t="n">
+        <v>-1023.659</v>
+      </c>
+      <c r="P181" s="12" t="n">
+        <v>-1568.373</v>
+      </c>
+      <c r="Q181" s="12" t="n">
+        <v>-1065.358</v>
+      </c>
+      <c r="R181" s="12" t="n">
+        <v>-933.15</v>
+      </c>
+      <c r="S181" s="12" t="n">
+        <v>541.319</v>
+      </c>
+      <c r="T181" s="12" t="n">
+        <v>-1255.745</v>
+      </c>
+      <c r="U181" s="12" t="n">
+        <v>2575.417</v>
+      </c>
+      <c r="V181" s="12" t="n">
+        <v>1498.486</v>
+      </c>
+      <c r="W181" s="12" t="n">
+        <v>-637.318</v>
+      </c>
+      <c r="X181" s="12" t="n">
+        <v>-3287.513</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E182" s="22" t="n">
+        <v>86.271</v>
+      </c>
+      <c r="I182" s="22" t="n">
+        <v>58.059</v>
+      </c>
+      <c r="M182" s="22" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="O182" s="22" t="n">
+        <v>-48.272</v>
+      </c>
+      <c r="P182" s="22" t="n">
+        <v>-19.457</v>
+      </c>
+      <c r="Q182" s="22" t="n">
+        <v>-24.537</v>
+      </c>
+      <c r="R182" s="22" t="n">
+        <v>-8.282999999999999</v>
+      </c>
+      <c r="S182" s="22" t="n">
+        <v>-23.911</v>
+      </c>
+      <c r="T182" s="22" t="n">
+        <v>80.834</v>
+      </c>
+      <c r="U182" s="22" t="n">
+        <v>126.966</v>
+      </c>
+      <c r="V182" s="22" t="n">
+        <v>86.271</v>
+      </c>
+      <c r="W182" s="22" t="n">
+        <v>58.059</v>
+      </c>
+      <c r="X182" s="22" t="n">
+        <v>59.61</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E176" s="22" t="n">
+      <c r="E183" s="22" t="n">
         <v>82.636</v>
       </c>
-      <c r="I176" s="22" t="n">
+      <c r="I183" s="22" t="n">
         <v>-179.952</v>
       </c>
-      <c r="M176" s="22" t="n">
+      <c r="M183" s="22" t="n">
         <v>615.13</v>
       </c>
-      <c r="O176" s="22" t="n">
+      <c r="O183" s="22" t="n">
         <v>217.535</v>
       </c>
-      <c r="P176" s="22" t="n">
+      <c r="P183" s="22" t="n">
         <v>-337.614</v>
       </c>
-      <c r="Q176" s="22" t="n">
+      <c r="Q183" s="22" t="n">
         <v>-197.052</v>
       </c>
-      <c r="R176" s="22" t="n">
+      <c r="R183" s="22" t="n">
         <v>437.353</v>
       </c>
-      <c r="S176" s="22" t="n">
+      <c r="S183" s="22" t="n">
         <v>2747.886</v>
       </c>
-      <c r="T176" s="22" t="n">
+      <c r="T183" s="22" t="n">
         <v>-104.628</v>
       </c>
-      <c r="U176" s="22" t="n">
+      <c r="U183" s="22" t="n">
         <v>-211.901</v>
       </c>
-      <c r="V176" s="22" t="n">
+      <c r="V183" s="22" t="n">
         <v>82.636</v>
       </c>
-      <c r="W176" s="22" t="n">
+      <c r="W183" s="22" t="n">
         <v>-179.952</v>
       </c>
-      <c r="X176" s="22" t="n">
+      <c r="X183" s="22" t="n">
         <v>615.13</v>
       </c>
     </row>
@@ -10151,7 +10622,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11593,7 +12064,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11645,7 +12116,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11697,7 +12168,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11749,7 +12220,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11801,7 +12272,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11853,7 +12324,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11905,7 +12376,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11915,43 +12386,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11975,7 +12446,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12027,7 +12498,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12079,7 +12550,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12131,7 +12602,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12183,7 +12654,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12235,7 +12706,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12305,7 +12776,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12357,7 +12828,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12367,49 +12838,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12419,49 +12890,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12471,49 +12942,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12523,43 +12994,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12583,7 +13054,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12635,7 +13106,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12687,7 +13158,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12739,7 +13210,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14779,24 +15250,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
